--- a/docs/act-three-alchemizr-tags.xlsx
+++ b/docs/act-three-alchemizr-tags.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="370">
   <si>
     <t xml:space="preserve">The Matrx Alchemizr — Act III Tag Assignment</t>
   </si>
@@ -101,6 +101,12 @@
     <t xml:space="preserve">act.three.tracks_updated_media_lyrics_UPDATED.xlsx, sheet "Updated Track Order" — joined to tracks BY TITLE, never by row position. Covers 21 of the 32 tracks.</t>
   </si>
   <si>
+    <t xml:space="preserve">Author-supplied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body Jumper lyrics, supplied directly by the author. The master lyric book carries only the line "Lyrics not present in the supplied master sources" under that title.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Set aside</t>
   </si>
   <si>
@@ -137,7 +143,7 @@
     <t xml:space="preserve">Body Jumper</t>
   </si>
   <si>
-    <t xml:space="preserve">Left untagged on purpose. No lyrics exist in any supplied source and both workbooks leave its taxonomy row blank, so any tag would be invention.</t>
+    <t xml:space="preserve">Tagged from author-supplied lyrics, and read as one track even though it runs Body Jumper into the Crucible Code section and an Act Four activation outro. It is the only track carrying four Vibe tags: the forensic verses (Dark, Hypnotic) and the ascension (Ethereal, Empowering) are two distinct modes, and collapsing them to three would drop a real one.</t>
   </si>
   <si>
     <t xml:space="preserve">Tag counts</t>
@@ -797,10 +803,25 @@
     <t xml:space="preserve">Promethean closer: "Transmutes the base to gold"; "Creation and destruction, both coded in my depth" — Polarity as stated duality. Frequency for "Hermetic current in the pulse". Fire alone; the song is nothing else.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unassigned — no source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNTAGGED — no evidence available. The lyric book prints "Lyrics not present in the supplied master sources" under this title, and both workbooks leave its taxonomy row blank. Needs lyrics or a manual call before tagging.</t>
+    <t xml:space="preserve">Dark, Hypnotic, Ethereal, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Transform, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth, Power, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Correspondence, Cause &amp; Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author-supplied lyrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite closer that runs possession-horror into integration and hands off to Act Four. Refusal of the entity ("I am not a host—I deny access"; "I am the axis at the gate") gives Protect; the repeated "Leave every borrowed voice / name / version" and "set my old self ablaze" give Release; "I walk out burned—But redesigned" gives Transform and Rebirth. Elements are named outright in the outro — "Fire refined. Now air defines." Correspondence for "The war was never outside me—it just wore a borrowed face / Every mimic that I banished was a mirror of my case"; Polarity for "I dissolve the last distinction between hunted and the hunter"; Cause &amp; Effect for "You don't disrupt the process—you become the documentation". Freedom for "walking through ungated doors" and the explicit end of the war; Power for melting the throne "down to the gold it was always structured under". Carries four Vibe tags — the only track that does — because the cold forensic verses (Dark, Hypnotic) and the Crucible Code ascension (Ethereal, Empowering) are genuinely two modes in one track.</t>
   </si>
   <si>
     <t xml:space="preserve">Tag columns C:G are the editable cells. Labels must match the Tag Dictionary sheet exactly; the database seed rejects anything else. Body Jumper is intentionally blank — no lyrics exist in any supplied source.</t>
@@ -965,7 +986,7 @@
     <t xml:space="preserve">Frequency</t>
   </si>
   <si>
-    <t xml:space="preserve">Share of Album is against the 31 tagged tracks; Body Jumper is excluded because it carries no tags. Counts use a substring match within the tag column for that category — safe here because no label in a category is a substring of another.</t>
+    <t xml:space="preserve">Share of Album is against every track on the Track Tags sheet. Counts use a substring match within the tag column for that category — safe here because no label in a category is a substring of another.</t>
   </si>
   <si>
     <t xml:space="preserve">Why the tags come from the lyric book and UPDATED.xlsx, and why CORRECTED2.xlsm was set aside.</t>
@@ -1058,7 +1079,7 @@
     <t xml:space="preserve">Tracks untagged</t>
   </si>
   <si>
-    <t xml:space="preserve">Body Jumper — no lyrics in any source.</t>
+    <t xml:space="preserve">Every track now carries tags.</t>
   </si>
   <si>
     <t xml:space="preserve">Total tag assignments</t>
@@ -1080,6 +1101,9 @@
   </si>
   <si>
     <t xml:space="preserve">No taxonomy row survives the title join for these.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body Jumper — lyrics provided directly, absent from the master lyric book.</t>
   </si>
   <si>
     <t xml:space="preserve">Vocabulary labels defined</t>
@@ -1185,7 +1209,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF8A6A3A"/>
       <name val="Arial"/>
@@ -1298,7 +1322,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1380,30 +1404,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1715,7 +1715,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1858,23 +1858,23 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="B24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
@@ -1906,6 +1906,14 @@
       </c>
       <c r="B28" s="4" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1941,47 +1949,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1989,35 +1997,35 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">IF(C5="",0,LEN(C5)-LEN(SUBSTITUTE(C5,",",""))+1)+IF(D5="",0,LEN(D5)-LEN(SUBSTITUTE(D5,",",""))+1)+IF(E5="",0,LEN(E5)-LEN(SUBSTITUTE(E5,",",""))+1)+IF(F5="",0,LEN(F5)-LEN(SUBSTITUTE(F5,",",""))+1)+IF(G5="",0,LEN(G5)-LEN(SUBSTITUTE(G5,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2025,35 +2033,35 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">IF(C6="",0,LEN(C6)-LEN(SUBSTITUTE(C6,",",""))+1)+IF(D6="",0,LEN(D6)-LEN(SUBSTITUTE(D6,",",""))+1)+IF(E6="",0,LEN(E6)-LEN(SUBSTITUTE(E6,",",""))+1)+IF(F6="",0,LEN(F6)-LEN(SUBSTITUTE(F6,",",""))+1)+IF(G6="",0,LEN(G6)-LEN(SUBSTITUTE(G6,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,35 +2069,35 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="false">IF(C7="",0,LEN(C7)-LEN(SUBSTITUTE(C7,",",""))+1)+IF(D7="",0,LEN(D7)-LEN(SUBSTITUTE(D7,",",""))+1)+IF(E7="",0,LEN(E7)-LEN(SUBSTITUTE(E7,",",""))+1)+IF(F7="",0,LEN(F7)-LEN(SUBSTITUTE(F7,",",""))+1)+IF(G7="",0,LEN(G7)-LEN(SUBSTITUTE(G7,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2097,35 +2105,35 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">IF(C8="",0,LEN(C8)-LEN(SUBSTITUTE(C8,",",""))+1)+IF(D8="",0,LEN(D8)-LEN(SUBSTITUTE(D8,",",""))+1)+IF(E8="",0,LEN(E8)-LEN(SUBSTITUTE(E8,",",""))+1)+IF(F8="",0,LEN(F8)-LEN(SUBSTITUTE(F8,",",""))+1)+IF(G8="",0,LEN(G8)-LEN(SUBSTITUTE(G8,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2133,35 +2141,35 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">IF(C9="",0,LEN(C9)-LEN(SUBSTITUTE(C9,",",""))+1)+IF(D9="",0,LEN(D9)-LEN(SUBSTITUTE(D9,",",""))+1)+IF(E9="",0,LEN(E9)-LEN(SUBSTITUTE(E9,",",""))+1)+IF(F9="",0,LEN(F9)-LEN(SUBSTITUTE(F9,",",""))+1)+IF(G9="",0,LEN(G9)-LEN(SUBSTITUTE(G9,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2169,35 +2177,35 @@
         <v>6</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">IF(C10="",0,LEN(C10)-LEN(SUBSTITUTE(C10,",",""))+1)+IF(D10="",0,LEN(D10)-LEN(SUBSTITUTE(D10,",",""))+1)+IF(E10="",0,LEN(E10)-LEN(SUBSTITUTE(E10,",",""))+1)+IF(F10="",0,LEN(F10)-LEN(SUBSTITUTE(F10,",",""))+1)+IF(G10="",0,LEN(G10)-LEN(SUBSTITUTE(G10,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2205,35 +2213,35 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H11" s="16" t="n">
         <f aca="false">IF(C11="",0,LEN(C11)-LEN(SUBSTITUTE(C11,",",""))+1)+IF(D11="",0,LEN(D11)-LEN(SUBSTITUTE(D11,",",""))+1)+IF(E11="",0,LEN(E11)-LEN(SUBSTITUTE(E11,",",""))+1)+IF(F11="",0,LEN(F11)-LEN(SUBSTITUTE(F11,",",""))+1)+IF(G11="",0,LEN(G11)-LEN(SUBSTITUTE(G11,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2241,35 +2249,35 @@
         <v>8</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">IF(C12="",0,LEN(C12)-LEN(SUBSTITUTE(C12,",",""))+1)+IF(D12="",0,LEN(D12)-LEN(SUBSTITUTE(D12,",",""))+1)+IF(E12="",0,LEN(E12)-LEN(SUBSTITUTE(E12,",",""))+1)+IF(F12="",0,LEN(F12)-LEN(SUBSTITUTE(F12,",",""))+1)+IF(G12="",0,LEN(G12)-LEN(SUBSTITUTE(G12,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2277,35 +2285,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false">IF(C13="",0,LEN(C13)-LEN(SUBSTITUTE(C13,",",""))+1)+IF(D13="",0,LEN(D13)-LEN(SUBSTITUTE(D13,",",""))+1)+IF(E13="",0,LEN(E13)-LEN(SUBSTITUTE(E13,",",""))+1)+IF(F13="",0,LEN(F13)-LEN(SUBSTITUTE(F13,",",""))+1)+IF(G13="",0,LEN(G13)-LEN(SUBSTITUTE(G13,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2313,35 +2321,35 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">IF(C14="",0,LEN(C14)-LEN(SUBSTITUTE(C14,",",""))+1)+IF(D14="",0,LEN(D14)-LEN(SUBSTITUTE(D14,",",""))+1)+IF(E14="",0,LEN(E14)-LEN(SUBSTITUTE(E14,",",""))+1)+IF(F14="",0,LEN(F14)-LEN(SUBSTITUTE(F14,",",""))+1)+IF(G14="",0,LEN(G14)-LEN(SUBSTITUTE(G14,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2349,35 +2357,35 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H15" s="16" t="n">
         <f aca="false">IF(C15="",0,LEN(C15)-LEN(SUBSTITUTE(C15,",",""))+1)+IF(D15="",0,LEN(D15)-LEN(SUBSTITUTE(D15,",",""))+1)+IF(E15="",0,LEN(E15)-LEN(SUBSTITUTE(E15,",",""))+1)+IF(F15="",0,LEN(F15)-LEN(SUBSTITUTE(F15,",",""))+1)+IF(G15="",0,LEN(G15)-LEN(SUBSTITUTE(G15,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2385,35 +2393,35 @@
         <v>12</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">IF(C16="",0,LEN(C16)-LEN(SUBSTITUTE(C16,",",""))+1)+IF(D16="",0,LEN(D16)-LEN(SUBSTITUTE(D16,",",""))+1)+IF(E16="",0,LEN(E16)-LEN(SUBSTITUTE(E16,",",""))+1)+IF(F16="",0,LEN(F16)-LEN(SUBSTITUTE(F16,",",""))+1)+IF(G16="",0,LEN(G16)-LEN(SUBSTITUTE(G16,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2421,35 +2429,35 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">IF(C17="",0,LEN(C17)-LEN(SUBSTITUTE(C17,",",""))+1)+IF(D17="",0,LEN(D17)-LEN(SUBSTITUTE(D17,",",""))+1)+IF(E17="",0,LEN(E17)-LEN(SUBSTITUTE(E17,",",""))+1)+IF(F17="",0,LEN(F17)-LEN(SUBSTITUTE(F17,",",""))+1)+IF(G17="",0,LEN(G17)-LEN(SUBSTITUTE(G17,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2457,35 +2465,35 @@
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IF(C18="",0,LEN(C18)-LEN(SUBSTITUTE(C18,",",""))+1)+IF(D18="",0,LEN(D18)-LEN(SUBSTITUTE(D18,",",""))+1)+IF(E18="",0,LEN(E18)-LEN(SUBSTITUTE(E18,",",""))+1)+IF(F18="",0,LEN(F18)-LEN(SUBSTITUTE(F18,",",""))+1)+IF(G18="",0,LEN(G18)-LEN(SUBSTITUTE(G18,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2493,35 +2501,35 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H19" s="16" t="n">
         <f aca="false">IF(C19="",0,LEN(C19)-LEN(SUBSTITUTE(C19,",",""))+1)+IF(D19="",0,LEN(D19)-LEN(SUBSTITUTE(D19,",",""))+1)+IF(E19="",0,LEN(E19)-LEN(SUBSTITUTE(E19,",",""))+1)+IF(F19="",0,LEN(F19)-LEN(SUBSTITUTE(F19,",",""))+1)+IF(G19="",0,LEN(G19)-LEN(SUBSTITUTE(G19,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2529,35 +2537,35 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">IF(C20="",0,LEN(C20)-LEN(SUBSTITUTE(C20,",",""))+1)+IF(D20="",0,LEN(D20)-LEN(SUBSTITUTE(D20,",",""))+1)+IF(E20="",0,LEN(E20)-LEN(SUBSTITUTE(E20,",",""))+1)+IF(F20="",0,LEN(F20)-LEN(SUBSTITUTE(F20,",",""))+1)+IF(G20="",0,LEN(G20)-LEN(SUBSTITUTE(G20,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2565,35 +2573,35 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">IF(C21="",0,LEN(C21)-LEN(SUBSTITUTE(C21,",",""))+1)+IF(D21="",0,LEN(D21)-LEN(SUBSTITUTE(D21,",",""))+1)+IF(E21="",0,LEN(E21)-LEN(SUBSTITUTE(E21,",",""))+1)+IF(F21="",0,LEN(F21)-LEN(SUBSTITUTE(F21,",",""))+1)+IF(G21="",0,LEN(G21)-LEN(SUBSTITUTE(G21,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2601,35 +2609,35 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">IF(C22="",0,LEN(C22)-LEN(SUBSTITUTE(C22,",",""))+1)+IF(D22="",0,LEN(D22)-LEN(SUBSTITUTE(D22,",",""))+1)+IF(E22="",0,LEN(E22)-LEN(SUBSTITUTE(E22,",",""))+1)+IF(F22="",0,LEN(F22)-LEN(SUBSTITUTE(F22,",",""))+1)+IF(G22="",0,LEN(G22)-LEN(SUBSTITUTE(G22,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2637,35 +2645,35 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">IF(C23="",0,LEN(C23)-LEN(SUBSTITUTE(C23,",",""))+1)+IF(D23="",0,LEN(D23)-LEN(SUBSTITUTE(D23,",",""))+1)+IF(E23="",0,LEN(E23)-LEN(SUBSTITUTE(E23,",",""))+1)+IF(F23="",0,LEN(F23)-LEN(SUBSTITUTE(F23,",",""))+1)+IF(G23="",0,LEN(G23)-LEN(SUBSTITUTE(G23,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2673,35 +2681,35 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H24" s="19" t="n">
         <f aca="false">IF(C24="",0,LEN(C24)-LEN(SUBSTITUTE(C24,",",""))+1)+IF(D24="",0,LEN(D24)-LEN(SUBSTITUTE(D24,",",""))+1)+IF(E24="",0,LEN(E24)-LEN(SUBSTITUTE(E24,",",""))+1)+IF(F24="",0,LEN(F24)-LEN(SUBSTITUTE(F24,",",""))+1)+IF(G24="",0,LEN(G24)-LEN(SUBSTITUTE(G24,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2709,35 +2717,35 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">IF(C25="",0,LEN(C25)-LEN(SUBSTITUTE(C25,",",""))+1)+IF(D25="",0,LEN(D25)-LEN(SUBSTITUTE(D25,",",""))+1)+IF(E25="",0,LEN(E25)-LEN(SUBSTITUTE(E25,",",""))+1)+IF(F25="",0,LEN(F25)-LEN(SUBSTITUTE(F25,",",""))+1)+IF(G25="",0,LEN(G25)-LEN(SUBSTITUTE(G25,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2745,35 +2753,35 @@
         <v>22</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H26" s="19" t="n">
         <f aca="false">IF(C26="",0,LEN(C26)-LEN(SUBSTITUTE(C26,",",""))+1)+IF(D26="",0,LEN(D26)-LEN(SUBSTITUTE(D26,",",""))+1)+IF(E26="",0,LEN(E26)-LEN(SUBSTITUTE(E26,",",""))+1)+IF(F26="",0,LEN(F26)-LEN(SUBSTITUTE(F26,",",""))+1)+IF(G26="",0,LEN(G26)-LEN(SUBSTITUTE(G26,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2781,35 +2789,35 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">IF(C27="",0,LEN(C27)-LEN(SUBSTITUTE(C27,",",""))+1)+IF(D27="",0,LEN(D27)-LEN(SUBSTITUTE(D27,",",""))+1)+IF(E27="",0,LEN(E27)-LEN(SUBSTITUTE(E27,",",""))+1)+IF(F27="",0,LEN(F27)-LEN(SUBSTITUTE(F27,",",""))+1)+IF(G27="",0,LEN(G27)-LEN(SUBSTITUTE(G27,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2817,35 +2825,35 @@
         <v>24</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H28" s="19" t="n">
         <f aca="false">IF(C28="",0,LEN(C28)-LEN(SUBSTITUTE(C28,",",""))+1)+IF(D28="",0,LEN(D28)-LEN(SUBSTITUTE(D28,",",""))+1)+IF(E28="",0,LEN(E28)-LEN(SUBSTITUTE(E28,",",""))+1)+IF(F28="",0,LEN(F28)-LEN(SUBSTITUTE(F28,",",""))+1)+IF(G28="",0,LEN(G28)-LEN(SUBSTITUTE(G28,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2853,35 +2861,35 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">IF(C29="",0,LEN(C29)-LEN(SUBSTITUTE(C29,",",""))+1)+IF(D29="",0,LEN(D29)-LEN(SUBSTITUTE(D29,",",""))+1)+IF(E29="",0,LEN(E29)-LEN(SUBSTITUTE(E29,",",""))+1)+IF(F29="",0,LEN(F29)-LEN(SUBSTITUTE(F29,",",""))+1)+IF(G29="",0,LEN(G29)-LEN(SUBSTITUTE(G29,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2889,35 +2897,35 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H30" s="19" t="n">
         <f aca="false">IF(C30="",0,LEN(C30)-LEN(SUBSTITUTE(C30,",",""))+1)+IF(D30="",0,LEN(D30)-LEN(SUBSTITUTE(D30,",",""))+1)+IF(E30="",0,LEN(E30)-LEN(SUBSTITUTE(E30,",",""))+1)+IF(F30="",0,LEN(F30)-LEN(SUBSTITUTE(F30,",",""))+1)+IF(G30="",0,LEN(G30)-LEN(SUBSTITUTE(G30,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2925,35 +2933,35 @@
         <v>27</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">IF(C31="",0,LEN(C31)-LEN(SUBSTITUTE(C31,",",""))+1)+IF(D31="",0,LEN(D31)-LEN(SUBSTITUTE(D31,",",""))+1)+IF(E31="",0,LEN(E31)-LEN(SUBSTITUTE(E31,",",""))+1)+IF(F31="",0,LEN(F31)-LEN(SUBSTITUTE(F31,",",""))+1)+IF(G31="",0,LEN(G31)-LEN(SUBSTITUTE(G31,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2961,35 +2969,35 @@
         <v>28</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H32" s="19" t="n">
         <f aca="false">IF(C32="",0,LEN(C32)-LEN(SUBSTITUTE(C32,",",""))+1)+IF(D32="",0,LEN(D32)-LEN(SUBSTITUTE(D32,",",""))+1)+IF(E32="",0,LEN(E32)-LEN(SUBSTITUTE(E32,",",""))+1)+IF(F32="",0,LEN(F32)-LEN(SUBSTITUTE(F32,",",""))+1)+IF(G32="",0,LEN(G32)-LEN(SUBSTITUTE(G32,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2997,35 +3005,35 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H33" s="16" t="n">
         <f aca="false">IF(C33="",0,LEN(C33)-LEN(SUBSTITUTE(C33,",",""))+1)+IF(D33="",0,LEN(D33)-LEN(SUBSTITUTE(D33,",",""))+1)+IF(E33="",0,LEN(E33)-LEN(SUBSTITUTE(E33,",",""))+1)+IF(F33="",0,LEN(F33)-LEN(SUBSTITUTE(F33,",",""))+1)+IF(G33="",0,LEN(G33)-LEN(SUBSTITUTE(G33,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3033,35 +3041,35 @@
         <v>30</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H34" s="19" t="n">
         <f aca="false">IF(C34="",0,LEN(C34)-LEN(SUBSTITUTE(C34,",",""))+1)+IF(D34="",0,LEN(D34)-LEN(SUBSTITUTE(D34,",",""))+1)+IF(E34="",0,LEN(E34)-LEN(SUBSTITUTE(E34,",",""))+1)+IF(F34="",0,LEN(F34)-LEN(SUBSTITUTE(F34,",",""))+1)+IF(G34="",0,LEN(G34)-LEN(SUBSTITUTE(G34,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3069,77 +3077,87 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H35" s="16" t="n">
         <f aca="false">IF(C35="",0,LEN(C35)-LEN(SUBSTITUTE(C35,",",""))+1)+IF(D35="",0,LEN(D35)-LEN(SUBSTITUTE(D35,",",""))+1)+IF(E35="",0,LEN(E35)-LEN(SUBSTITUTE(E35,",",""))+1)+IF(F35="",0,LEN(F35)-LEN(SUBSTITUTE(F35,",",""))+1)+IF(G35="",0,LEN(G35)-LEN(SUBSTITUTE(G35,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="20" t="n">
+      <c r="B36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="H36" s="19" t="n">
         <f aca="false">IF(C36="",0,LEN(C36)-LEN(SUBSTITUTE(C36,",",""))+1)+IF(D36="",0,LEN(D36)-LEN(SUBSTITUTE(D36,",",""))+1)+IF(E36="",0,LEN(E36)-LEN(SUBSTITUTE(E36,",",""))+1)+IF(F36="",0,LEN(F36)-LEN(SUBSTITUTE(F36,",",""))+1)+IF(G36="",0,LEN(G36)-LEN(SUBSTITUTE(G36,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>258</v>
+        <v>15</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
+      <c r="A38" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3198,794 +3216,794 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="31" t="n">
+      <c r="A5" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B5&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="E5" s="32" t="n">
-        <f aca="false">IFERROR(D5/31,0)</f>
-        <v>0.0645161290322581</v>
+      <c r="E5" s="26" t="n">
+        <f aca="false">IFERROR(D5/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="31" t="n">
+      <c r="A6" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B6&amp;"*")</f>
         <v>5</v>
       </c>
-      <c r="E6" s="32" t="n">
-        <f aca="false">IFERROR(D6/31,0)</f>
-        <v>0.161290322580645</v>
+      <c r="E6" s="26" t="n">
+        <f aca="false">IFERROR(D6/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7" s="31" t="n">
+      <c r="A7" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B7&amp;"*")</f>
-        <v>18</v>
-      </c>
-      <c r="E7" s="32" t="n">
-        <f aca="false">IFERROR(D7/31,0)</f>
-        <v>0.580645161290323</v>
+        <v>19</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <f aca="false">IFERROR(D7/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="31" t="n">
+      <c r="A8" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B8&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="E8" s="32" t="n">
-        <f aca="false">IFERROR(D8/31,0)</f>
-        <v>0.0645161290322581</v>
+      <c r="E8" s="26" t="n">
+        <f aca="false">IFERROR(D8/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D9" s="31" t="n">
+      <c r="A9" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D9" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B9&amp;"*")</f>
         <v>19</v>
       </c>
-      <c r="E9" s="32" t="n">
-        <f aca="false">IFERROR(D9/31,0)</f>
-        <v>0.612903225806452</v>
+      <c r="E9" s="26" t="n">
+        <f aca="false">IFERROR(D9/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B10" s="29" t="s">
+      <c r="A10" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D10" s="31" t="n">
+      <c r="B10" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B10&amp;"*")</f>
-        <v>10</v>
-      </c>
-      <c r="E10" s="32" t="n">
-        <f aca="false">IFERROR(D10/31,0)</f>
-        <v>0.32258064516129</v>
+        <v>11</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <f aca="false">IFERROR(D10/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>274</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D11" s="31" t="n">
+      <c r="A11" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B11&amp;"*")</f>
         <v>8</v>
       </c>
-      <c r="E11" s="32" t="n">
-        <f aca="false">IFERROR(D11/31,0)</f>
-        <v>0.258064516129032</v>
+      <c r="E11" s="26" t="n">
+        <f aca="false">IFERROR(D11/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="C12" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B12&amp;"*")</f>
-        <v>10</v>
-      </c>
-      <c r="E12" s="32" t="n">
-        <f aca="false">IFERROR(D12/31,0)</f>
-        <v>0.32258064516129</v>
+        <v>11</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <f aca="false">IFERROR(D12/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="31" t="n">
+      <c r="A13" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B13&amp;"*")</f>
-        <v>14</v>
-      </c>
-      <c r="E13" s="32" t="n">
-        <f aca="false">IFERROR(D13/31,0)</f>
-        <v>0.451612903225806</v>
+        <v>15</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <f aca="false">IFERROR(D13/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D14" s="31" t="n">
+      <c r="A14" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B14&amp;"*")</f>
         <v>5</v>
       </c>
-      <c r="E14" s="32" t="n">
-        <f aca="false">IFERROR(D14/31,0)</f>
-        <v>0.161290322580645</v>
+      <c r="E14" s="26" t="n">
+        <f aca="false">IFERROR(D14/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D15" s="31" t="n">
+      <c r="A15" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D15" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B15&amp;"*")</f>
         <v>6</v>
       </c>
-      <c r="E15" s="32" t="n">
-        <f aca="false">IFERROR(D15/31,0)</f>
-        <v>0.193548387096774</v>
+      <c r="E15" s="26" t="n">
+        <f aca="false">IFERROR(D15/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D16" s="31" t="n">
+      <c r="A16" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B16&amp;"*")</f>
-        <v>10</v>
-      </c>
-      <c r="E16" s="32" t="n">
-        <f aca="false">IFERROR(D16/31,0)</f>
-        <v>0.32258064516129</v>
+        <v>11</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <f aca="false">IFERROR(D16/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D17" s="31" t="n">
+      <c r="A17" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D17" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B17&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E17" s="32" t="n">
-        <f aca="false">IFERROR(D17/31,0)</f>
-        <v>0.225806451612903</v>
+      <c r="E17" s="26" t="n">
+        <f aca="false">IFERROR(D17/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D18" s="31" t="n">
+      <c r="A18" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B18&amp;"*")</f>
         <v>8</v>
       </c>
-      <c r="E18" s="32" t="n">
-        <f aca="false">IFERROR(D18/31,0)</f>
-        <v>0.258064516129032</v>
+      <c r="E18" s="26" t="n">
+        <f aca="false">IFERROR(D18/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="C19" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D19" s="31" t="n">
+      <c r="B19" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B19&amp;"*")</f>
-        <v>13</v>
-      </c>
-      <c r="E19" s="32" t="n">
-        <f aca="false">IFERROR(D19/31,0)</f>
-        <v>0.419354838709677</v>
+        <v>14</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <f aca="false">IFERROR(D19/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D20" s="31" t="n">
+      <c r="A20" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D20" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B20&amp;"*")</f>
-        <v>8</v>
-      </c>
-      <c r="E20" s="32" t="n">
-        <f aca="false">IFERROR(D20/31,0)</f>
-        <v>0.258064516129032</v>
+        <v>9</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <f aca="false">IFERROR(D20/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>286</v>
       </c>
-      <c r="C21" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B21&amp;"*")</f>
         <v>3</v>
       </c>
-      <c r="E21" s="32" t="n">
-        <f aca="false">IFERROR(D21/31,0)</f>
-        <v>0.0967741935483871</v>
+      <c r="E21" s="26" t="n">
+        <f aca="false">IFERROR(D21/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D22" s="31" t="n">
+      <c r="A22" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D22" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B22&amp;"*")</f>
         <v>8</v>
       </c>
-      <c r="E22" s="32" t="n">
-        <f aca="false">IFERROR(D22/31,0)</f>
-        <v>0.258064516129032</v>
+      <c r="E22" s="26" t="n">
+        <f aca="false">IFERROR(D22/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D23" s="31" t="n">
+      <c r="A23" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D23" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B23&amp;"*")</f>
         <v>13</v>
       </c>
-      <c r="E23" s="32" t="n">
-        <f aca="false">IFERROR(D23/31,0)</f>
-        <v>0.419354838709677</v>
+      <c r="E23" s="26" t="n">
+        <f aca="false">IFERROR(D23/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D24" s="31" t="n">
+      <c r="A24" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B24&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E24" s="32" t="n">
-        <f aca="false">IFERROR(D24/31,0)</f>
-        <v>0.225806451612903</v>
+      <c r="E24" s="26" t="n">
+        <f aca="false">IFERROR(D24/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D25" s="31" t="n">
+      <c r="A25" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B25&amp;"*")</f>
-        <v>15</v>
-      </c>
-      <c r="E25" s="32" t="n">
-        <f aca="false">IFERROR(D25/31,0)</f>
-        <v>0.483870967741936</v>
+        <v>16</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <f aca="false">IFERROR(D25/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D26" s="31" t="n">
+      <c r="A26" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="D26" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B26&amp;"*")</f>
         <v>9</v>
       </c>
-      <c r="E26" s="32" t="n">
-        <f aca="false">IFERROR(D26/31,0)</f>
-        <v>0.290322580645161</v>
+      <c r="E26" s="26" t="n">
+        <f aca="false">IFERROR(D26/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D27" s="31" t="n">
+      <c r="A27" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B27&amp;"*")</f>
-        <v>14</v>
-      </c>
-      <c r="E27" s="32" t="n">
-        <f aca="false">IFERROR(D27/31,0)</f>
-        <v>0.451612903225806</v>
+        <v>15</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <f aca="false">IFERROR(D27/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D28" s="31" t="n">
+      <c r="A28" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="D28" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B28&amp;"*")</f>
         <v>19</v>
       </c>
-      <c r="E28" s="32" t="n">
-        <f aca="false">IFERROR(D28/31,0)</f>
-        <v>0.612903225806452</v>
+      <c r="E28" s="26" t="n">
+        <f aca="false">IFERROR(D28/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D29" s="31" t="n">
+      <c r="A29" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D29" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B29&amp;"*")</f>
-        <v>12</v>
-      </c>
-      <c r="E29" s="32" t="n">
-        <f aca="false">IFERROR(D29/31,0)</f>
-        <v>0.387096774193548</v>
+        <v>13</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <f aca="false">IFERROR(D29/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D30" s="31" t="n">
+      <c r="A30" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D30" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B30&amp;"*")</f>
-        <v>16</v>
-      </c>
-      <c r="E30" s="32" t="n">
-        <f aca="false">IFERROR(D30/31,0)</f>
-        <v>0.516129032258065</v>
+        <v>17</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <f aca="false">IFERROR(D30/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D31" s="31" t="n">
+      <c r="A31" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D31" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B31&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E31" s="32" t="n">
-        <f aca="false">IFERROR(D31/31,0)</f>
-        <v>0.354838709677419</v>
+      <c r="E31" s="26" t="n">
+        <f aca="false">IFERROR(D31/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D32" s="31" t="n">
+      <c r="A32" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D32" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B32&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E32" s="32" t="n">
-        <f aca="false">IFERROR(D32/31,0)</f>
-        <v>0.354838709677419</v>
+      <c r="E32" s="26" t="n">
+        <f aca="false">IFERROR(D32/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D33" s="31" t="n">
+      <c r="A33" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D33" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B33&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E33" s="32" t="n">
-        <f aca="false">IFERROR(D33/31,0)</f>
-        <v>0.225806451612903</v>
+      <c r="E33" s="26" t="n">
+        <f aca="false">IFERROR(D33/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B34" s="29" t="s">
+      <c r="A34" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D34" s="31" t="n">
+      <c r="B34" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D34" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B34&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E34" s="32" t="n">
-        <f aca="false">IFERROR(D34/31,0)</f>
-        <v>0.354838709677419</v>
+      <c r="E34" s="26" t="n">
+        <f aca="false">IFERROR(D34/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D35" s="31" t="n">
+      <c r="A35" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D35" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B35&amp;"*")</f>
-        <v>12</v>
-      </c>
-      <c r="E35" s="32" t="n">
-        <f aca="false">IFERROR(D35/31,0)</f>
-        <v>0.387096774193548</v>
+        <v>13</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <f aca="false">IFERROR(D35/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="B36" s="29" t="s">
+      <c r="A36" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C36" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="C36" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D36" s="31" t="n">
+      <c r="D36" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B36&amp;"*")</f>
         <v>5</v>
       </c>
-      <c r="E36" s="32" t="n">
-        <f aca="false">IFERROR(D36/31,0)</f>
-        <v>0.161290322580645</v>
+      <c r="E36" s="26" t="n">
+        <f aca="false">IFERROR(D36/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D37" s="31" t="n">
+      <c r="A37" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D37" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B37&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E37" s="32" t="n">
-        <f aca="false">IFERROR(D37/31,0)</f>
-        <v>0.225806451612903</v>
+      <c r="E37" s="26" t="n">
+        <f aca="false">IFERROR(D37/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>306</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D38" s="31" t="n">
+      <c r="A38" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D38" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B38&amp;"*")</f>
-        <v>5</v>
-      </c>
-      <c r="E38" s="32" t="n">
-        <f aca="false">IFERROR(D38/31,0)</f>
-        <v>0.161290322580645</v>
+        <v>6</v>
+      </c>
+      <c r="E38" s="26" t="n">
+        <f aca="false">IFERROR(D38/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D39" s="31" t="n">
+      <c r="A39" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D39" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B39&amp;"*")</f>
-        <v>14</v>
-      </c>
-      <c r="E39" s="32" t="n">
-        <f aca="false">IFERROR(D39/31,0)</f>
-        <v>0.451612903225806</v>
+        <v>15</v>
+      </c>
+      <c r="E39" s="26" t="n">
+        <f aca="false">IFERROR(D39/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B40" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D40" s="31" t="n">
+      <c r="A40" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D40" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B40&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E40" s="32" t="n">
-        <f aca="false">IFERROR(D40/31,0)</f>
-        <v>0.225806451612903</v>
+      <c r="E40" s="26" t="n">
+        <f aca="false">IFERROR(D40/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B41" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D41" s="31" t="n">
+      <c r="A41" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D41" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B41&amp;"*")</f>
-        <v>16</v>
-      </c>
-      <c r="E41" s="32" t="n">
-        <f aca="false">IFERROR(D41/31,0)</f>
-        <v>0.516129032258065</v>
+        <v>17</v>
+      </c>
+      <c r="E41" s="26" t="n">
+        <f aca="false">IFERROR(D41/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B42" s="29" t="s">
+      <c r="A42" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C42" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D42" s="31" t="n">
+      <c r="B42" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D42" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B42&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="E42" s="32" t="n">
-        <f aca="false">IFERROR(D42/31,0)</f>
-        <v>0.0645161290322581</v>
+      <c r="E42" s="26" t="n">
+        <f aca="false">IFERROR(D42/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B43" s="29" t="s">
-        <v>311</v>
-      </c>
-      <c r="C43" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D43" s="31" t="n">
+      <c r="A43" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D43" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B43&amp;"*")</f>
         <v>4</v>
       </c>
-      <c r="E43" s="32" t="n">
-        <f aca="false">IFERROR(D43/31,0)</f>
-        <v>0.129032258064516</v>
+      <c r="E43" s="26" t="n">
+        <f aca="false">IFERROR(D43/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.125</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B44" s="29" t="s">
+      <c r="A44" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="C44" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D44" s="31" t="n">
+      <c r="D44" s="25" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B44&amp;"*")</f>
         <v>9</v>
       </c>
-      <c r="E44" s="32" t="n">
-        <f aca="false">IFERROR(D44/31,0)</f>
-        <v>0.290322580645161</v>
+      <c r="E44" s="26" t="n">
+        <f aca="false">IFERROR(D44/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
+      <c r="A46" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4020,61 +4038,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>317</v>
+        <v>323</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>319</v>
+        <v>325</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>321</v>
+        <v>327</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>323</v>
+        <v>329</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>325</v>
+        <v>331</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>327</v>
+        <v>333</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4083,32 +4101,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>330</v>
+        <v>336</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>332</v>
+        <v>338</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>334</v>
+        <v>340</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -4127,7 +4145,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -4142,191 +4160,203 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="B5" s="38" t="n">
+      <c r="A5" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="32" t="n">
         <f aca="false">COUNTA('Track Tags'!$B$5:$B$36)</f>
         <v>32</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="B6" s="38" t="n">
+      <c r="A6" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="32" t="n">
         <f aca="false">COUNTIF('Track Tags'!$H$5:$H$36,"&gt;0")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="B7" s="38" t="n">
+      <c r="A7" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="32" t="n">
         <f aca="false">COUNTIF('Track Tags'!$H$5:$H$36,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="B8" s="38" t="n">
+      <c r="A8" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="B8" s="32" t="n">
         <f aca="false">SUM('Track Tags'!$H$5:$H$36)</f>
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B9" s="39" t="n">
+      <c r="A9" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="B9" s="33" t="n">
         <f aca="false">IFERROR(B8/B6,0)</f>
-        <v>12.3225806451613</v>
+        <v>12.40625</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="B10" s="38" t="n">
+      <c r="A10" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="B10" s="32" t="n">
         <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Lyric book + workbook")</f>
         <v>21</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="38" t="n">
+      <c r="A11" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="32" t="n">
         <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Lyric book only")</f>
         <v>10</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>352</v>
-      </c>
-      <c r="B12" s="38" t="n">
+      <c r="A12" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="32" t="n">
+        <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Author-supplied lyrics")</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="32" t="n">
         <f aca="false">COUNTA('Tag Dictionary'!$B$5:$B$44)</f>
         <v>40</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="B13" s="38" t="n">
+      <c r="C13" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="B14" s="32" t="n">
         <f aca="false">COUNTIF('Tag Dictionary'!$D$5:$D$44,"&gt;0")</f>
         <v>40</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="40" t="s">
-        <v>356</v>
+      <c r="C14" s="10" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="38" t="n">
+      <c r="A16" s="34" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="32" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$C$5:$C$36)-LEN(SUBSTITUTE('Track Tags'!$C$5:$C$36,",","")))+((LEN('Track Tags'!$C$5:$C$36)&gt;0)*1))</f>
+        <v>92</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="32" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$D$5:$D$36)-LEN(SUBSTITUTE('Track Tags'!$D$5:$D$36,",","")))+((LEN('Track Tags'!$D$5:$D$36)&gt;0)*1))</f>
+        <v>91</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="32" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$E$5:$E$36)-LEN(SUBSTITUTE('Track Tags'!$E$5:$E$36,",","")))+((LEN('Track Tags'!$E$5:$E$36)&gt;0)*1))</f>
+        <v>59</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="32" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$F$5:$F$36)-LEN(SUBSTITUTE('Track Tags'!$F$5:$F$36,",","")))+((LEN('Track Tags'!$F$5:$F$36)&gt;0)*1))</f>
         <v>88</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="38" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$D$5:$D$36)-LEN(SUBSTITUTE('Track Tags'!$D$5:$D$36,",","")))+((LEN('Track Tags'!$D$5:$D$36)&gt;0)*1))</f>
-        <v>88</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="38" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$E$5:$E$36)-LEN(SUBSTITUTE('Track Tags'!$E$5:$E$36,",","")))+((LEN('Track Tags'!$E$5:$E$36)&gt;0)*1))</f>
-        <v>57</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="38" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$F$5:$F$36)-LEN(SUBSTITUTE('Track Tags'!$F$5:$F$36,",","")))+((LEN('Track Tags'!$F$5:$F$36)&gt;0)*1))</f>
-        <v>85</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="38" t="n">
+      <c r="C20" s="10" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="32" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$G$5:$G$36)-LEN(SUBSTITUTE('Track Tags'!$G$5:$G$36,",","")))+((LEN('Track Tags'!$G$5:$G$36)&gt;0)*1))</f>
-        <v>64</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>361</v>
+        <v>67</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/docs/act-three-alchemizr-tags.xlsx
+++ b/docs/act-three-alchemizr-tags.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="365">
   <si>
     <t xml:space="preserve">The Matrx Alchemizr — Act III Tag Assignment</t>
   </si>
@@ -101,12 +101,6 @@
     <t xml:space="preserve">act.three.tracks_updated_media_lyrics_UPDATED.xlsx, sheet "Updated Track Order" — joined to tracks BY TITLE, never by row position. Covers 21 of the 32 tracks.</t>
   </si>
   <si>
-    <t xml:space="preserve">Author-supplied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Body Jumper lyrics, supplied directly by the author. The master lyric book carries only the line "Lyrics not present in the supplied master sources" under that title.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Set aside</t>
   </si>
   <si>
@@ -140,670 +134,667 @@
     <t xml:space="preserve">Follows the design document: Heartbreak sits in Intention, Empowering in Vibe, so a cathartic-not-sad pairing is expressible. Applied to the betrayal tracks.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tag counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roughly 2-3 tags per category per track, applied uniformly. Fewer tags make a track easier to score 100% on; more tags dilute each one. Nothing in the sources fixes this number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Track Tags — Act III "Reclamation"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow columns are editable. Total Tags and all QA figures are formulas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Track Title (public.tracks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vibe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vibration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence Basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workbook Taxonomy (title-matched)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why These Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome To The Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gritty, Empowering, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Transform, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Legacy, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyric book + workbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiation Through Fire | Invocation + Awakening | emberCore/ceremonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stolen authorship and betrayal turned into ignition: "thank you for the fire / I didn't know I needed it to rise"; "I'm taking back my authorship now". Polarity for the betrayal-to-rise inversion, Frequency for "feeding her my frequency".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reclamation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Gritty, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Transform, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, Power, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resonance, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Reclamation | Resurrection + Reclamation | goldenSignal/ceremonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrongful confinement and return: "fifty days ticking", "this is reclamation, the day Musiq Matrix came back". Earth for the cage/box, Resonance for "my voice is the code", Polarity for "the bigger the cage, the louder the call".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Know Your Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Hypnotic, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus, Protect, Awaken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air, Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative Manipulation | Exposure + Warning | buriedTruth/tectonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold forensic naming: "I logged the tremors before the quake was admitted", "domino logic listen, then swing". Air for "every signal hums through the wires", Earth for cold-storage archive (workbook: buriedTruth/tectonic).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold On Through The Burial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Gritty, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal, Inspire, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth, Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhythm, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hope Against Collapse | Lament + Alignment | deepMemoryVault/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endurance anthem: "the same dirt meant to bury you can raise you up again". Earth for burial/ground, Water for "the rain came down like judgment" (workbook motion: ripple). Rhythm for the night-to-dawn cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chosen Ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethereal, Hypnotic, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Inspire, Connect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, Rebirth, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency, Resonance, Mentalism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective Awakening | Awakening + Alignment | goldenSignal/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation-breach awakening: "you cracked the first encryption they installed inside your brain", "a frequency for seekers". Mentalism for the installed-encryption framing, Air for lattices of lightning/broadcast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete Warnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protect, Awaken, Educate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loyalty, War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Rhythm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyric book only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street prophecy warning a friend about betrayers in his own ranks: "the concrete's got ears". Earth for concrete/paved-over ground, Cause &amp; Effect and Rhythm for "history repeats, a pattern etched in pain". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjacent (Reroute It)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Educate, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, Power, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authority Restoration | Override + Invocation | redSignalStorm/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gatekeeping answered by routing around it: "No seat? I'm building the table around it". Educate for the Les Paul / tape-loop history lesson; Cause &amp; Effect for "every era repeats the same tired design".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art! Official!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euphoric, Empowering, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Educate, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air, Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy, Faith, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency, Correspondence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI defended as sacred craft: "I plug into the cosmos, download divine semantics", "prophetic frequencies". Correspondence for "where circuitry meets soul / divine by design". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thought Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypnotic, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Awaken, Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentalism, Correspondence, Cause &amp; Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal Transmission | Invocation + Alignment | orbitalMind/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The album's explicit Mentalism lecture: "The first Hermetic principle is not love... It is Mind"; "As above, so below was never just a phrase"; "You are the code beneath the cause" (workbook skin: orbitalMind).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remember the Price (When You Speak the Name)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Transform, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy, Rebirth, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow work priced out loud: "I audited the dark", "I metabolized hell so you could access the best", "just remember the price when you speak the name". Fire for the torch handed forward. Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint of the Divine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethereal, Euphoric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Educate, Connect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correspondence, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divine Remembering | Invocation + Command Sequence | celestialGrid/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four-movement prayer pattern "written before time, stitched into the design"; "how the signal travels, how the frequency finds home". Correspondence for the inherited-pattern structure (workbook: celestialGrid).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flip It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Hypnotic, Euphoric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform, Heal, Educate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth, Freedom, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Mentalism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The album's purest Polarity track — the mechanic is literal reversal: "E-V-I-L L-I-V-E", "stressed" to "desserts", "the wound is where the gift begins", "the difference is the direction that you choose to read". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Am the Signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Hypnotic, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Focus, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Freedom, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency, Resonance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"I am the signal / I am the frequency / I am the sound"; "coherence is the warfare"; "incoherent energy can't find a match"; "frequency is the protection". Earth for "built underground... channel it through the ground". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Create as I Speak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euphoric, Empowering, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Inspire, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentalism, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher Self Activation | Command Sequence + Momentum Surge | goldenSignal/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoken-word manifestation: "Each line is a law. I create as I speak"; "Abracadabra, I act like it's done". Mentalism for speech-as-cause; Frequency for "innovation ain't just sound, it's a frequency streak".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As Above, So Below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty, Hypnotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Educate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Faith, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correspondence, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal Transmission | Alignment + Invocation | celestialGrid/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correspondence is the title and the thesis; Polarity for the sustained heaven/hell inversion: "I seen Heaven in a cell and Hell in a mansion", "One mind... two wars". Earth for "thrones in the trenches".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elemental Orchestra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal, Connect, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Legacy, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, Resonance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotional Resurrection | Emotional Archive + Ascension | deepMemoryVault/ceremonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asking to be witnessed, then becoming the witness: "I didn't need a crown. I needed a witness"; "You do not wait for flowers. You are the bloom." Gender for that self-generative turn — the Kybalion principle of the generative force acting within one being (workbook particles: lightFilaments + waterDroplets).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Witness Don’t Talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypnotic, Ethereal, Chill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Educate, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal Transmission | Awakening + Command Sequence | deepMemoryVault/hypnotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The observer self as recording architecture: "The Witness don't talk it transmits"; "you just finally found the frequency it sits". Workbook motion style is literally "hypnotic"; skin is deepMemoryVault (archive = Legacy).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Schemes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Nostalgic, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Heal, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Loyalty, War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Cause &amp; Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacred Memory | Memory Echo + Purification | bureaucraticInferno/volatile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A bond corrupted by third-party influence, held open anyway: "still trying to hold a space for your redemption arc"; "even demons bend when faced with light". Polarity for that light/dark hinge; Water for the sustained grief.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Through the Fog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Dreamy, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Protect, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Loyalty, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longing | Memory Echo + Lament | submergedSignal/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love held behind a boundary: "I love you... but safety's the altar my soul answers to"; "a lighthouse still burning long after the storm". Water is unambiguous — fog, flood, waves, mist (workbook: submergedSignal/ripple).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gritty, Nostalgic, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loyalty, Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrepaid loyalty demanded back: "Where the hell are my flowers? / For the nights I held your soul power". Rhythm for the month-by-month calendar close ("September, you left / October came in cold"). Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misguided Priorities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty, Nostalgic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Protect, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, War, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grief Processing | Reflection + Lament | liquidMirror/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grief redirected at the other's fate: "My grief ain't for myself now, it's for your soul alone"; "I can see the price you'll pay for gambling with your soul". Freedom for "all my fucking sovereignty" (workbook: liquidMirror/ripple/waterDroplets confirms Water).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hierophant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Awaken, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, War, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Mentalism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritual War | Reflection + Awakening | liquidMirror/hypnotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">States the principle outright: "This isn't a curse it's cause and effect, a shadow that forms where light gets neglect"; "the Ten of Swords sits lodged in his spine". Mentalism for "the voice that his conscience designed".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foolish Pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Dark, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Heal, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Loyalty, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withholding as self-inflicted ruin: "You built an altar to withholding"; "the lessons that protected you became the bars you couldn't see". Earth and Rhythm for "the grave grows flowers too, long after the ground above goes still". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where the Phantom Fell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Ethereal, Nostalgic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cautionary elegy: "mercy needs choosing and love needs belief / and he traded them both for the crown of a thief"; "don't follow the path where the phantom fell". Polarity for "mistook his own heaven for hell". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Whole Cost of You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Dreamy, Chill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Heal, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Rebirth, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, Rhythm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure by burying an invented version of someone: "I know I wrote him myself, line after line in red". Gender for that generative projection — a figure authored inside the self; Rhythm for "the tower falls so the tower can be free". Fire for "let it go up like smoke, let it go up like a flame". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Without Stains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protect, Release, Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truth Broadcast | Confession + Transmutation | crucibleEngine/volatile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A staged ritual ambush survived: "They wanted blood without stains"; "You can't drain a soul that was never yours to claim". Fire from the workbook crucibleEngine/ash/burningPaper treatment; Earth for the body as vessel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slumlord Fundamentalists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gritty, Dark, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Freedom, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institutional Corruption | Exposure + Indictment | bureaucraticInferno/militant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentary indictment of housing corruption: "constructive eviction", "welfare fraud", "every empire crumbles, that's the fatal flaw". Earth alone — the whole song is buildings, locks, heat and habitable space. Rhythm for the September-to-February sequence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reckoning Already Rolled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Empowering, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consequence stated as already-completed: "The reckoning isn't incoming / the reckoning already rolled". Mentalism for "I sharpen clarity like a scalpel / I don't chase you; I undo you". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architect of the Aftermath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Protect, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth, Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Correspondence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Sovereignty | Alignment + Transmutation | celestialGrid/tectonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forensic account of an illegal eviction: "I am the Architect of the Aftermath / mapping fault lines in your rigged collapse"; "the blueprint indicts your method in the light". Correspondence for blueprint-mirrors-territory (workbook motion: tectonic confirms Earth).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seer Broke Chains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Protect, Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, War, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritual War | Revolt + Transmutation | containmentFailure/volatile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curse reversed on its sender: "I sabotage, reverse the code"; "now every curse turns back to me"; "I walked through fire, I broke your chains". Water for "the sea returns where fire once flowed".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire in My Veins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform, Manifest, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Rebirth, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Reclamation | Transmutation + Ascension | emberCore/ember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promethean closer: "Transmutes the base to gold"; "Creation and destruction, both coded in my depth" — Polarity as stated duality. Frequency for "Hermetic current in the pulse". Fire alone; the song is nothing else.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Body Jumper</t>
   </si>
   <si>
-    <t xml:space="preserve">Tagged from author-supplied lyrics, and read as one track even though it runs Body Jumper into the Crucible Code section and an Act Four activation outro. It is the only track carrying four Vibe tags: the forensic verses (Dark, Hypnotic) and the ascension (Ethereal, Empowering) are two distinct modes, and collapsing them to three would drop a real one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag counts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roughly 2-3 tags per category per track. Fewer tags make a track easier to score 100% on; more tags dilute each one. Nothing in the sources fixes this number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Tags — Act III "Reclamation"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow columns are editable. Total Tags and all QA figures are formulas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Title (public.tracks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vibe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vibration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence Basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workbook Taxonomy (title-matched)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why These Tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welcome To The Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gritty, Empowering, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Transform, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, Legacy, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polarity, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyric book + workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initiation Through Fire | Invocation + Awakening | emberCore/ceremonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stolen authorship and betrayal turned into ignition: "thank you for the fire / I didn't know I needed it to rise"; "I'm taking back my authorship now". Polarity for the betrayal-to-rise inversion, Frequency for "feeding her my frequency".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reclamation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Gritty, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Transform, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire, Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, Power, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resonance, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Reclamation | Resurrection + Reclamation | goldenSignal/ceremonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrongful confinement and return: "fifty days ticking", "this is reclamation, the day Musiq Matrix came back". Earth for the cage/box, Resonance for "my voice is the code", Polarity for "the bigger the cage, the louder the call".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Know Your Names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Hypnotic, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focus, Protect, Awaken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air, Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative Manipulation | Exposure + Warning | buriedTruth/tectonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cold forensic naming: "I logged the tremors before the quake was admitted", "domino logic listen, then swing". Air for "every signal hums through the wires", Earth for cold-storage archive (workbook: buriedTruth/tectonic).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold On Through The Burial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Gritty, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heal, Inspire, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth, Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhythm, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hope Against Collapse | Lament + Alignment | deepMemoryVault/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endurance anthem: "the same dirt meant to bury you can raise you up again". Earth for burial/ground, Water for "the rain came down like judgment" (workbook motion: ripple). Rhythm for the night-to-dawn cycle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chosen Ones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethereal, Hypnotic, Empowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Inspire, Connect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, Rebirth, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency, Resonance, Mentalism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collective Awakening | Awakening + Alignment | goldenSignal/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation-breach awakening: "you cracked the first encryption they installed inside your brain", "a frequency for seekers". Mentalism for the installed-encryption framing, Air for lattices of lightning/broadcast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete Warnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protect, Awaken, Educate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth, Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loyalty, War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Rhythm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyric book only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street prophecy warning a friend about betrayers in his own ranks: "the concrete's got ears". Earth for concrete/paved-over ground, Cause &amp; Effect and Rhythm for "history repeats, a pattern etched in pain". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjacent (Reroute It)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Educate, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, Power, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authority Restoration | Override + Invocation | redSignalStorm/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gatekeeping answered by routing around it: "No seat? I'm building the table around it". Educate for the Les Paul / tape-loop history lesson; Cause &amp; Effect for "every era repeats the same tired design".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art! Official!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euphoric, Empowering, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Educate, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air, Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy, Faith, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency, Correspondence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI defended as sacred craft: "I plug into the cosmos, download divine semantics", "prophetic frequencies". Correspondence for "where circuitry meets soul / divine by design". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thought Form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypnotic, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Awaken, Transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentalism, Correspondence, Cause &amp; Effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal Transmission | Invocation + Alignment | orbitalMind/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The album's explicit Mentalism lecture: "The first Hermetic principle is not love... It is Mind"; "As above, so below was never just a phrase"; "You are the code beneath the cause" (workbook skin: orbitalMind).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remember the Price (When You Speak the Name)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty, Empowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Transform, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy, Rebirth, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow work priced out loud: "I audited the dark", "I metabolized hell so you could access the best", "just remember the price when you speak the name". Fire for the torch handed forward. Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint of the Divine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethereal, Euphoric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Educate, Connect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondence, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divine Remembering | Invocation + Command Sequence | celestialGrid/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four-movement prayer pattern "written before time, stitched into the design"; "how the signal travels, how the frequency finds home". Correspondence for the inherited-pattern structure (workbook: celestialGrid).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flip It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Hypnotic, Euphoric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform, Heal, Educate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth, Freedom, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polarity, Mentalism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The album's purest Polarity track — the mechanic is literal reversal: "E-V-I-L L-I-V-E", "stressed" to "desserts", "the wound is where the gift begins", "the difference is the direction that you choose to read". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Am the Signal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Hypnotic, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Focus, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, Freedom, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency, Resonance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"I am the signal / I am the frequency / I am the sound"; "coherence is the warfare"; "incoherent energy can't find a match"; "frequency is the protection". Earth for "built underground... channel it through the ground". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Create as I Speak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euphoric, Empowering, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Inspire, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentalism, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higher Self Activation | Command Sequence + Momentum Surge | goldenSignal/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spoken-word manifestation: "Each line is a law. I create as I speak"; "Abracadabra, I act like it's done". Mentalism for speech-as-cause; Frequency for "innovation ain't just sound, it's a frequency streak".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Above, So Below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty, Hypnotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Educate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Faith, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondence, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal Transmission | Alignment + Invocation | celestialGrid/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondence is the title and the thesis; Polarity for the sustained heaven/hell inversion: "I seen Heaven in a cell and Hell in a mansion", "One mind... two wars". Earth for "thrones in the trenches".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elemental Orchestra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heal, Connect, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water, Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Legacy, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender, Resonance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emotional Resurrection | Emotional Archive + Ascension | deepMemoryVault/ceremonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asking to be witnessed, then becoming the witness: "I didn't need a crown. I needed a witness"; "You do not wait for flowers. You are the bloom." Gender for that self-generative turn — the Kybalion principle of the generative force acting within one being (workbook particles: lightFilaments + waterDroplets).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Witness Don’t Talk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypnotic, Ethereal, Chill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Educate, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal Transmission | Awakening + Command Sequence | deepMemoryVault/hypnotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The observer self as recording architecture: "The Witness don't talk it transmits"; "you just finally found the frequency it sits". Workbook motion style is literally "hypnotic"; skin is deepMemoryVault (archive = Legacy).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonic Schemes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Nostalgic, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Heal, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water, Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Loyalty, War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polarity, Cause &amp; Effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sacred Memory | Memory Echo + Purification | bureaucraticInferno/volatile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A bond corrupted by third-party influence, held open anyway: "still trying to hold a space for your redemption arc"; "even demons bend when faced with light". Polarity for that light/dark hinge; Water for the sustained grief.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Through the Fog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Dreamy, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Protect, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water, Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Loyalty, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longing | Memory Echo + Lament | submergedSignal/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love held behind a boundary: "I love you... but safety's the altar my soul answers to"; "a lighthouse still burning long after the storm". Water is unambiguous — fog, flood, waves, mist (workbook: submergedSignal/ripple).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flowers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gritty, Nostalgic, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loyalty, Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unrepaid loyalty demanded back: "Where the hell are my flowers? / For the nights I held your soul power". Rhythm for the month-by-month calendar close ("September, you left / October came in cold"). Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Misguided Priorities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty, Nostalgic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Protect, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, War, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grief Processing | Reflection + Lament | liquidMirror/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grief redirected at the other's fate: "My grief ain't for myself now, it's for your soul alone"; "I can see the price you'll pay for gambling with your soul". Freedom for "all my fucking sovereignty" (workbook: liquidMirror/ripple/waterDroplets confirms Water).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hierophant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Awaken, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, War, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Mentalism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiritual War | Reflection + Awakening | liquidMirror/hypnotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States the principle outright: "This isn't a curse it's cause and effect, a shadow that forms where light gets neglect"; "the Ten of Swords sits lodged in his spine". Mentalism for "the voice that his conscience designed".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foolish Pride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Dark, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Heal, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Loyalty, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withholding as self-inflicted ruin: "You built an altar to withholding"; "the lessons that protected you became the bars you couldn't see". Earth and Rhythm for "the grave grows flowers too, long after the ground above goes still". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where the Phantom Fell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Ethereal, Nostalgic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A cautionary elegy: "mercy needs choosing and love needs belief / and he traded them both for the crown of a thief"; "don't follow the path where the phantom fell". Polarity for "mistook his own heaven for hell". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Whole Cost of You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Dreamy, Chill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Heal, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Rebirth, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender, Rhythm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closure by burying an invented version of someone: "I know I wrote him myself, line after line in red". Gender for that generative projection — a figure authored inside the self; Rhythm for "the tower falls so the tower can be free". Fire for "let it go up like smoke, let it go up like a flame". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood Without Stains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protect, Release, Transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truth Broadcast | Confession + Transmutation | crucibleEngine/volatile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A staged ritual ambush survived: "They wanted blood without stains"; "You can't drain a soul that was never yours to claim". Fire from the workbook crucibleEngine/ash/burningPaper treatment; Earth for the body as vessel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slumlord Fundamentalists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gritty, Dark, Empowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Freedom, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institutional Corruption | Exposure + Indictment | bureaucraticInferno/militant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentary indictment of housing corruption: "constructive eviction", "welfare fraud", "every empire crumbles, that's the fatal flaw". Earth alone — the whole song is buildings, locks, heat and habitable space. Rhythm for the September-to-February sequence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reckoning Already Rolled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Empowering, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focus, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consequence stated as already-completed: "The reckoning isn't incoming / the reckoning already rolled". Mentalism for "I sharpen clarity like a scalpel / I don't chase you; I undo you". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architect of the Aftermath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Protect, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth, Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Correspondence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal Sovereignty | Alignment + Transmutation | celestialGrid/tectonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forensic account of an illegal eviction: "I am the Architect of the Aftermath / mapping fault lines in your rigged collapse"; "the blueprint indicts your method in the light". Correspondence for blueprint-mirrors-territory (workbook motion: tectonic confirms Earth).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seer Broke Chains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Protect, Transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire, Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, War, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiritual War | Revolt + Transmutation | containmentFailure/volatile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curse reversed on its sender: "I sabotage, reverse the code"; "now every curse turns back to me"; "I walked through fire, I broke your chains". Water for "the sea returns where fire once flowed".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire in My Veins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform, Manifest, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, Rebirth, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Reclamation | Transmutation + Ascension | emberCore/ember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promethean closer: "Transmutes the base to gold"; "Creation and destruction, both coded in my depth" — Polarity as stated duality. Frequency for "Hermetic current in the pulse". Fire alone; the song is nothing else.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Hypnotic, Ethereal, Empowering</t>
+    <t xml:space="preserve">Dark, Hypnotic, Empowering</t>
   </si>
   <si>
     <t xml:space="preserve">Release, Transform, Protect</t>
@@ -818,10 +809,7 @@
     <t xml:space="preserve">Polarity, Correspondence, Cause &amp; Effect</t>
   </si>
   <si>
-    <t xml:space="preserve">Author-supplied lyrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composite closer that runs possession-horror into integration and hands off to Act Four. Refusal of the entity ("I am not a host—I deny access"; "I am the axis at the gate") gives Protect; the repeated "Leave every borrowed voice / name / version" and "set my old self ablaze" give Release; "I walk out burned—But redesigned" gives Transform and Rebirth. Elements are named outright in the outro — "Fire refined. Now air defines." Correspondence for "The war was never outside me—it just wore a borrowed face / Every mimic that I banished was a mirror of my case"; Polarity for "I dissolve the last distinction between hunted and the hunter"; Cause &amp; Effect for "You don't disrupt the process—you become the documentation". Freedom for "walking through ungated doors" and the explicit end of the war; Power for melting the throne "down to the gold it was always structured under". Carries four Vibe tags — the only track that does — because the cold forensic verses (Dark, Hypnotic) and the Crucible Code ascension (Ethereal, Empowering) are genuinely two modes in one track.</t>
+    <t xml:space="preserve">Possession refused, then integrated: "I am not a host—I deny access"; "I am the axis at the gate" give Protect; the repeated "Leave every borrowed voice / name / version" and "set my old self ablaze" give Release; "I walk out burned—But redesigned" gives Transform and Rebirth. Elements are named outright in the outro — "Fire refined. Now air defines." Correspondence for "The war was never outside me—it just wore a borrowed face / Every mimic that I banished was a mirror of my case"; Polarity for "I dissolve the last distinction between hunted and the hunter"; Cause &amp; Effect for "You don't disrupt the process—you become the documentation". Freedom for "walking through ungated doors" and the explicit end of the war; Power for melting the throne "down to the gold it was always structured under".</t>
   </si>
   <si>
     <t xml:space="preserve">Tag columns C:G are the editable cells. Labels must match the Tag Dictionary sheet exactly; the database seed rejects anything else. Body Jumper is intentionally blank — no lyrics exist in any supplied source.</t>
@@ -1079,7 +1067,7 @@
     <t xml:space="preserve">Tracks untagged</t>
   </si>
   <si>
-    <t xml:space="preserve">Every track now carries tags.</t>
+    <t xml:space="preserve">Every track carries tags.</t>
   </si>
   <si>
     <t xml:space="preserve">Total tag assignments</t>
@@ -1101,9 +1089,6 @@
   </si>
   <si>
     <t xml:space="preserve">No taxonomy row survives the title join for these.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Body Jumper — lyrics provided directly, absent from the master lyric book.</t>
   </si>
   <si>
     <t xml:space="preserve">Vocabulary labels defined</t>
@@ -1146,7 +1131,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1204,14 +1189,6 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1F1B16"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF8A6A3A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1322,7 +1299,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1403,10 +1380,6 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1485,7 +1458,7 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF8A6A3A"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFD8CDBC"/>
@@ -1715,7 +1688,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1858,23 +1831,23 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
@@ -1898,22 +1871,6 @@
       </c>
       <c r="B27" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1949,47 +1906,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1997,35 +1954,35 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="G5" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>60</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">IF(C5="",0,LEN(C5)-LEN(SUBSTITUTE(C5,",",""))+1)+IF(D5="",0,LEN(D5)-LEN(SUBSTITUTE(D5,",",""))+1)+IF(E5="",0,LEN(E5)-LEN(SUBSTITUTE(E5,",",""))+1)+IF(F5="",0,LEN(F5)-LEN(SUBSTITUTE(F5,",",""))+1)+IF(G5="",0,LEN(G5)-LEN(SUBSTITUTE(G5,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,35 +1990,35 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="G6" s="15" t="s">
         <v>65</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>69</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">IF(C6="",0,LEN(C6)-LEN(SUBSTITUTE(C6,",",""))+1)+IF(D6="",0,LEN(D6)-LEN(SUBSTITUTE(D6,",",""))+1)+IF(E6="",0,LEN(E6)-LEN(SUBSTITUTE(E6,",",""))+1)+IF(F6="",0,LEN(F6)-LEN(SUBSTITUTE(F6,",",""))+1)+IF(G6="",0,LEN(G6)-LEN(SUBSTITUTE(G6,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2069,35 +2026,35 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="G7" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>77</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="false">IF(C7="",0,LEN(C7)-LEN(SUBSTITUTE(C7,",",""))+1)+IF(D7="",0,LEN(D7)-LEN(SUBSTITUTE(D7,",",""))+1)+IF(E7="",0,LEN(E7)-LEN(SUBSTITUTE(E7,",",""))+1)+IF(F7="",0,LEN(F7)-LEN(SUBSTITUTE(F7,",",""))+1)+IF(G7="",0,LEN(G7)-LEN(SUBSTITUTE(G7,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2105,35 +2062,35 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="G8" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">IF(C8="",0,LEN(C8)-LEN(SUBSTITUTE(C8,",",""))+1)+IF(D8="",0,LEN(D8)-LEN(SUBSTITUTE(D8,",",""))+1)+IF(E8="",0,LEN(E8)-LEN(SUBSTITUTE(E8,",",""))+1)+IF(F8="",0,LEN(F8)-LEN(SUBSTITUTE(F8,",",""))+1)+IF(G8="",0,LEN(G8)-LEN(SUBSTITUTE(G8,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2141,35 +2098,35 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="G9" s="15" t="s">
         <v>89</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>93</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">IF(C9="",0,LEN(C9)-LEN(SUBSTITUTE(C9,",",""))+1)+IF(D9="",0,LEN(D9)-LEN(SUBSTITUTE(D9,",",""))+1)+IF(E9="",0,LEN(E9)-LEN(SUBSTITUTE(E9,",",""))+1)+IF(F9="",0,LEN(F9)-LEN(SUBSTITUTE(F9,",",""))+1)+IF(G9="",0,LEN(G9)-LEN(SUBSTITUTE(G9,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2177,35 +2134,35 @@
         <v>6</v>
       </c>
       <c r="B10" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="G10" s="15" t="s">
         <v>97</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>101</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">IF(C10="",0,LEN(C10)-LEN(SUBSTITUTE(C10,",",""))+1)+IF(D10="",0,LEN(D10)-LEN(SUBSTITUTE(D10,",",""))+1)+IF(E10="",0,LEN(E10)-LEN(SUBSTITUTE(E10,",",""))+1)+IF(F10="",0,LEN(F10)-LEN(SUBSTITUTE(F10,",",""))+1)+IF(G10="",0,LEN(G10)-LEN(SUBSTITUTE(G10,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2213,35 +2170,35 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>105</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>109</v>
       </c>
       <c r="H11" s="16" t="n">
         <f aca="false">IF(C11="",0,LEN(C11)-LEN(SUBSTITUTE(C11,",",""))+1)+IF(D11="",0,LEN(D11)-LEN(SUBSTITUTE(D11,",",""))+1)+IF(E11="",0,LEN(E11)-LEN(SUBSTITUTE(E11,",",""))+1)+IF(F11="",0,LEN(F11)-LEN(SUBSTITUTE(F11,",",""))+1)+IF(G11="",0,LEN(G11)-LEN(SUBSTITUTE(G11,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2249,35 +2206,35 @@
         <v>8</v>
       </c>
       <c r="B12" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="G12" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>117</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">IF(C12="",0,LEN(C12)-LEN(SUBSTITUTE(C12,",",""))+1)+IF(D12="",0,LEN(D12)-LEN(SUBSTITUTE(D12,",",""))+1)+IF(E12="",0,LEN(E12)-LEN(SUBSTITUTE(E12,",",""))+1)+IF(F12="",0,LEN(F12)-LEN(SUBSTITUTE(F12,",",""))+1)+IF(G12="",0,LEN(G12)-LEN(SUBSTITUTE(G12,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,35 +2242,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>119</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>123</v>
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false">IF(C13="",0,LEN(C13)-LEN(SUBSTITUTE(C13,",",""))+1)+IF(D13="",0,LEN(D13)-LEN(SUBSTITUTE(D13,",",""))+1)+IF(E13="",0,LEN(E13)-LEN(SUBSTITUTE(E13,",",""))+1)+IF(F13="",0,LEN(F13)-LEN(SUBSTITUTE(F13,",",""))+1)+IF(G13="",0,LEN(G13)-LEN(SUBSTITUTE(G13,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,35 +2278,35 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">IF(C14="",0,LEN(C14)-LEN(SUBSTITUTE(C14,",",""))+1)+IF(D14="",0,LEN(D14)-LEN(SUBSTITUTE(D14,",",""))+1)+IF(E14="",0,LEN(E14)-LEN(SUBSTITUTE(E14,",",""))+1)+IF(F14="",0,LEN(F14)-LEN(SUBSTITUTE(F14,",",""))+1)+IF(G14="",0,LEN(G14)-LEN(SUBSTITUTE(G14,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2357,35 +2314,35 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>135</v>
       </c>
       <c r="H15" s="16" t="n">
         <f aca="false">IF(C15="",0,LEN(C15)-LEN(SUBSTITUTE(C15,",",""))+1)+IF(D15="",0,LEN(D15)-LEN(SUBSTITUTE(D15,",",""))+1)+IF(E15="",0,LEN(E15)-LEN(SUBSTITUTE(E15,",",""))+1)+IF(F15="",0,LEN(F15)-LEN(SUBSTITUTE(F15,",",""))+1)+IF(G15="",0,LEN(G15)-LEN(SUBSTITUTE(G15,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2393,35 +2350,35 @@
         <v>12</v>
       </c>
       <c r="B16" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>138</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>142</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">IF(C16="",0,LEN(C16)-LEN(SUBSTITUTE(C16,",",""))+1)+IF(D16="",0,LEN(D16)-LEN(SUBSTITUTE(D16,",",""))+1)+IF(E16="",0,LEN(E16)-LEN(SUBSTITUTE(E16,",",""))+1)+IF(F16="",0,LEN(F16)-LEN(SUBSTITUTE(F16,",",""))+1)+IF(G16="",0,LEN(G16)-LEN(SUBSTITUTE(G16,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2429,35 +2386,35 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>144</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>148</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">IF(C17="",0,LEN(C17)-LEN(SUBSTITUTE(C17,",",""))+1)+IF(D17="",0,LEN(D17)-LEN(SUBSTITUTE(D17,",",""))+1)+IF(E17="",0,LEN(E17)-LEN(SUBSTITUTE(E17,",",""))+1)+IF(F17="",0,LEN(F17)-LEN(SUBSTITUTE(F17,",",""))+1)+IF(G17="",0,LEN(G17)-LEN(SUBSTITUTE(G17,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2465,35 +2422,35 @@
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IF(C18="",0,LEN(C18)-LEN(SUBSTITUTE(C18,",",""))+1)+IF(D18="",0,LEN(D18)-LEN(SUBSTITUTE(D18,",",""))+1)+IF(E18="",0,LEN(E18)-LEN(SUBSTITUTE(E18,",",""))+1)+IF(F18="",0,LEN(F18)-LEN(SUBSTITUTE(F18,",",""))+1)+IF(G18="",0,LEN(G18)-LEN(SUBSTITUTE(G18,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2501,35 +2458,35 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>156</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>160</v>
       </c>
       <c r="H19" s="16" t="n">
         <f aca="false">IF(C19="",0,LEN(C19)-LEN(SUBSTITUTE(C19,",",""))+1)+IF(D19="",0,LEN(D19)-LEN(SUBSTITUTE(D19,",",""))+1)+IF(E19="",0,LEN(E19)-LEN(SUBSTITUTE(E19,",",""))+1)+IF(F19="",0,LEN(F19)-LEN(SUBSTITUTE(F19,",",""))+1)+IF(G19="",0,LEN(G19)-LEN(SUBSTITUTE(G19,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2537,35 +2494,35 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="G20" s="15" t="s">
         <v>164</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>168</v>
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">IF(C20="",0,LEN(C20)-LEN(SUBSTITUTE(C20,",",""))+1)+IF(D20="",0,LEN(D20)-LEN(SUBSTITUTE(D20,",",""))+1)+IF(E20="",0,LEN(E20)-LEN(SUBSTITUTE(E20,",",""))+1)+IF(F20="",0,LEN(F20)-LEN(SUBSTITUTE(F20,",",""))+1)+IF(G20="",0,LEN(G20)-LEN(SUBSTITUTE(G20,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2573,35 +2530,35 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">IF(C21="",0,LEN(C21)-LEN(SUBSTITUTE(C21,",",""))+1)+IF(D21="",0,LEN(D21)-LEN(SUBSTITUTE(D21,",",""))+1)+IF(E21="",0,LEN(E21)-LEN(SUBSTITUTE(E21,",",""))+1)+IF(F21="",0,LEN(F21)-LEN(SUBSTITUTE(F21,",",""))+1)+IF(G21="",0,LEN(G21)-LEN(SUBSTITUTE(G21,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2609,35 +2566,35 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="G22" s="15" t="s">
         <v>178</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>182</v>
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">IF(C22="",0,LEN(C22)-LEN(SUBSTITUTE(C22,",",""))+1)+IF(D22="",0,LEN(D22)-LEN(SUBSTITUTE(D22,",",""))+1)+IF(E22="",0,LEN(E22)-LEN(SUBSTITUTE(E22,",",""))+1)+IF(F22="",0,LEN(F22)-LEN(SUBSTITUTE(F22,",",""))+1)+IF(G22="",0,LEN(G22)-LEN(SUBSTITUTE(G22,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2645,35 +2602,35 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>189</v>
-      </c>
       <c r="G23" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">IF(C23="",0,LEN(C23)-LEN(SUBSTITUTE(C23,",",""))+1)+IF(D23="",0,LEN(D23)-LEN(SUBSTITUTE(D23,",",""))+1)+IF(E23="",0,LEN(E23)-LEN(SUBSTITUTE(E23,",",""))+1)+IF(F23="",0,LEN(F23)-LEN(SUBSTITUTE(F23,",",""))+1)+IF(G23="",0,LEN(G23)-LEN(SUBSTITUTE(G23,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,35 +2638,35 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H24" s="19" t="n">
         <f aca="false">IF(C24="",0,LEN(C24)-LEN(SUBSTITUTE(C24,",",""))+1)+IF(D24="",0,LEN(D24)-LEN(SUBSTITUTE(D24,",",""))+1)+IF(E24="",0,LEN(E24)-LEN(SUBSTITUTE(E24,",",""))+1)+IF(F24="",0,LEN(F24)-LEN(SUBSTITUTE(F24,",",""))+1)+IF(G24="",0,LEN(G24)-LEN(SUBSTITUTE(G24,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,35 +2674,35 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">IF(C25="",0,LEN(C25)-LEN(SUBSTITUTE(C25,",",""))+1)+IF(D25="",0,LEN(D25)-LEN(SUBSTITUTE(D25,",",""))+1)+IF(E25="",0,LEN(E25)-LEN(SUBSTITUTE(E25,",",""))+1)+IF(F25="",0,LEN(F25)-LEN(SUBSTITUTE(F25,",",""))+1)+IF(G25="",0,LEN(G25)-LEN(SUBSTITUTE(G25,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2753,35 +2710,35 @@
         <v>22</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H26" s="19" t="n">
         <f aca="false">IF(C26="",0,LEN(C26)-LEN(SUBSTITUTE(C26,",",""))+1)+IF(D26="",0,LEN(D26)-LEN(SUBSTITUTE(D26,",",""))+1)+IF(E26="",0,LEN(E26)-LEN(SUBSTITUTE(E26,",",""))+1)+IF(F26="",0,LEN(F26)-LEN(SUBSTITUTE(F26,",",""))+1)+IF(G26="",0,LEN(G26)-LEN(SUBSTITUTE(G26,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2789,35 +2746,35 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">IF(C27="",0,LEN(C27)-LEN(SUBSTITUTE(C27,",",""))+1)+IF(D27="",0,LEN(D27)-LEN(SUBSTITUTE(D27,",",""))+1)+IF(E27="",0,LEN(E27)-LEN(SUBSTITUTE(E27,",",""))+1)+IF(F27="",0,LEN(F27)-LEN(SUBSTITUTE(F27,",",""))+1)+IF(G27="",0,LEN(G27)-LEN(SUBSTITUTE(G27,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2825,35 +2782,35 @@
         <v>24</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H28" s="19" t="n">
         <f aca="false">IF(C28="",0,LEN(C28)-LEN(SUBSTITUTE(C28,",",""))+1)+IF(D28="",0,LEN(D28)-LEN(SUBSTITUTE(D28,",",""))+1)+IF(E28="",0,LEN(E28)-LEN(SUBSTITUTE(E28,",",""))+1)+IF(F28="",0,LEN(F28)-LEN(SUBSTITUTE(F28,",",""))+1)+IF(G28="",0,LEN(G28)-LEN(SUBSTITUTE(G28,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,35 +2818,35 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G29" s="15" t="s">
         <v>219</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>223</v>
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">IF(C29="",0,LEN(C29)-LEN(SUBSTITUTE(C29,",",""))+1)+IF(D29="",0,LEN(D29)-LEN(SUBSTITUTE(D29,",",""))+1)+IF(E29="",0,LEN(E29)-LEN(SUBSTITUTE(E29,",",""))+1)+IF(F29="",0,LEN(F29)-LEN(SUBSTITUTE(F29,",",""))+1)+IF(G29="",0,LEN(G29)-LEN(SUBSTITUTE(G29,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2897,35 +2854,35 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H30" s="19" t="n">
         <f aca="false">IF(C30="",0,LEN(C30)-LEN(SUBSTITUTE(C30,",",""))+1)+IF(D30="",0,LEN(D30)-LEN(SUBSTITUTE(D30,",",""))+1)+IF(E30="",0,LEN(E30)-LEN(SUBSTITUTE(E30,",",""))+1)+IF(F30="",0,LEN(F30)-LEN(SUBSTITUTE(F30,",",""))+1)+IF(G30="",0,LEN(G30)-LEN(SUBSTITUTE(G30,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2933,35 +2890,35 @@
         <v>27</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">IF(C31="",0,LEN(C31)-LEN(SUBSTITUTE(C31,",",""))+1)+IF(D31="",0,LEN(D31)-LEN(SUBSTITUTE(D31,",",""))+1)+IF(E31="",0,LEN(E31)-LEN(SUBSTITUTE(E31,",",""))+1)+IF(F31="",0,LEN(F31)-LEN(SUBSTITUTE(F31,",",""))+1)+IF(G31="",0,LEN(G31)-LEN(SUBSTITUTE(G31,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2969,35 +2926,35 @@
         <v>28</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H32" s="19" t="n">
         <f aca="false">IF(C32="",0,LEN(C32)-LEN(SUBSTITUTE(C32,",",""))+1)+IF(D32="",0,LEN(D32)-LEN(SUBSTITUTE(D32,",",""))+1)+IF(E32="",0,LEN(E32)-LEN(SUBSTITUTE(E32,",",""))+1)+IF(F32="",0,LEN(F32)-LEN(SUBSTITUTE(F32,",",""))+1)+IF(G32="",0,LEN(G32)-LEN(SUBSTITUTE(G32,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3005,35 +2962,35 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G33" s="15" t="s">
         <v>241</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>245</v>
       </c>
       <c r="H33" s="16" t="n">
         <f aca="false">IF(C33="",0,LEN(C33)-LEN(SUBSTITUTE(C33,",",""))+1)+IF(D33="",0,LEN(D33)-LEN(SUBSTITUTE(D33,",",""))+1)+IF(E33="",0,LEN(E33)-LEN(SUBSTITUTE(E33,",",""))+1)+IF(F33="",0,LEN(F33)-LEN(SUBSTITUTE(F33,",",""))+1)+IF(G33="",0,LEN(G33)-LEN(SUBSTITUTE(G33,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3041,35 +2998,35 @@
         <v>30</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H34" s="19" t="n">
         <f aca="false">IF(C34="",0,LEN(C34)-LEN(SUBSTITUTE(C34,",",""))+1)+IF(D34="",0,LEN(D34)-LEN(SUBSTITUTE(D34,",",""))+1)+IF(E34="",0,LEN(E34)-LEN(SUBSTITUTE(E34,",",""))+1)+IF(F34="",0,LEN(F34)-LEN(SUBSTITUTE(F34,",",""))+1)+IF(G34="",0,LEN(G34)-LEN(SUBSTITUTE(G34,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3077,87 +3034,87 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H35" s="16" t="n">
         <f aca="false">IF(C35="",0,LEN(C35)-LEN(SUBSTITUTE(C35,",",""))+1)+IF(D35="",0,LEN(D35)-LEN(SUBSTITUTE(D35,",",""))+1)+IF(E35="",0,LEN(E35)-LEN(SUBSTITUTE(E35,",",""))+1)+IF(F35="",0,LEN(F35)-LEN(SUBSTITUTE(F35,",",""))+1)+IF(G35="",0,LEN(G35)-LEN(SUBSTITUTE(G35,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>38</v>
+        <v>255</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F36" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="G36" s="15" t="s">
         <v>260</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>263</v>
       </c>
       <c r="H36" s="19" t="n">
         <f aca="false">IF(C36="",0,LEN(C36)-LEN(SUBSTITUTE(C36,",",""))+1)+IF(D36="",0,LEN(D36)-LEN(SUBSTITUTE(D36,",",""))+1)+IF(E36="",0,LEN(E36)-LEN(SUBSTITUTE(E36,",",""))+1)+IF(F36="",0,LEN(F36)-LEN(SUBSTITUTE(F36,",",""))+1)+IF(G36="",0,LEN(G36)-LEN(SUBSTITUTE(G36,",",""))+1)</f>
-        <v>15</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>264</v>
+        <v>14</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>98</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
+      <c r="A38" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3216,794 +3173,794 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B5" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C5" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B5&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="25" t="n">
         <f aca="false">IFERROR(D5/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.0625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="25" t="n">
+      <c r="A6" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B6&amp;"*")</f>
         <v>5</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">IFERROR(D6/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.15625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D7" s="25" t="n">
+      <c r="C7" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B7&amp;"*")</f>
         <v>19</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">IFERROR(D7/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.59375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="25" t="n">
+      <c r="A8" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B8&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">IFERROR(D8/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.0625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="C9" s="24" t="s">
+      <c r="A9" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="C9" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B9&amp;"*")</f>
         <v>19</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">IFERROR(D9/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.59375</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="25" t="n">
+      <c r="A10" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B10&amp;"*")</f>
-        <v>11</v>
-      </c>
-      <c r="E10" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
         <f aca="false">IFERROR(D10/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
-        <v>0.34375</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D11" s="25" t="n">
+      <c r="A11" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B11&amp;"*")</f>
         <v>8</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">IFERROR(D11/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D12" s="25" t="n">
+      <c r="A12" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B12&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="25" t="n">
         <f aca="false">IFERROR(D12/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.34375</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D13" s="25" t="n">
+      <c r="A13" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B13&amp;"*")</f>
         <v>15</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">IFERROR(D13/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.46875</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D14" s="25" t="n">
+      <c r="A14" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B14&amp;"*")</f>
         <v>5</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="25" t="n">
         <f aca="false">IFERROR(D14/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.15625</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D15" s="25" t="n">
+      <c r="A15" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D15" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B15&amp;"*")</f>
         <v>6</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">IFERROR(D15/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D16" s="25" t="n">
+      <c r="C16" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D16" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B16&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="25" t="n">
         <f aca="false">IFERROR(D16/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.34375</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D17" s="25" t="n">
+      <c r="A17" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D17" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B17&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="25" t="n">
         <f aca="false">IFERROR(D17/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.21875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C18" s="24" t="s">
+      <c r="A18" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="C18" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D18" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B18&amp;"*")</f>
         <v>8</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <f aca="false">IFERROR(D18/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D19" s="25" t="n">
+      <c r="A19" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D19" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B19&amp;"*")</f>
         <v>14</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <f aca="false">IFERROR(D19/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.4375</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D20" s="25" t="n">
+      <c r="A20" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B20&amp;"*")</f>
         <v>9</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="25" t="n">
         <f aca="false">IFERROR(D20/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.28125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D21" s="25" t="n">
+      <c r="A21" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B21&amp;"*")</f>
         <v>3</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="25" t="n">
         <f aca="false">IFERROR(D21/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.09375</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D22" s="25" t="n">
+      <c r="A22" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B22&amp;"*")</f>
         <v>8</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="25" t="n">
         <f aca="false">IFERROR(D22/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="25" t="n">
+      <c r="A23" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B23&amp;"*")</f>
         <v>13</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="25" t="n">
         <f aca="false">IFERROR(D23/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.40625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D24" s="25" t="n">
+      <c r="A24" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D24" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B24&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="25" t="n">
         <f aca="false">IFERROR(D24/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.21875</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="D25" s="25" t="n">
+      <c r="A25" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B25&amp;"*")</f>
         <v>16</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="25" t="n">
         <f aca="false">IFERROR(D25/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="D26" s="25" t="n">
+      <c r="A26" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D26" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B26&amp;"*")</f>
         <v>9</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="25" t="n">
         <f aca="false">IFERROR(D26/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.28125</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="D27" s="25" t="n">
+      <c r="A27" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B27&amp;"*")</f>
         <v>15</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="25" t="n">
         <f aca="false">IFERROR(D27/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.46875</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="D28" s="25" t="n">
+      <c r="A28" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D28" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B28&amp;"*")</f>
         <v>19</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="25" t="n">
         <f aca="false">IFERROR(D28/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.59375</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D29" s="25" t="n">
+      <c r="A29" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B29&amp;"*")</f>
         <v>13</v>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="25" t="n">
         <f aca="false">IFERROR(D29/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.40625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D30" s="25" t="n">
+      <c r="A30" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D30" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B30&amp;"*")</f>
         <v>17</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="25" t="n">
         <f aca="false">IFERROR(D30/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.53125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B31" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="B31" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D31" s="25" t="n">
+      <c r="C31" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B31&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E31" s="26" t="n">
+      <c r="E31" s="25" t="n">
         <f aca="false">IFERROR(D31/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.34375</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D32" s="25" t="n">
+      <c r="A32" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D32" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B32&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="25" t="n">
         <f aca="false">IFERROR(D32/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.34375</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="C33" s="24" t="s">
+      <c r="A33" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="D33" s="25" t="n">
+      <c r="C33" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D33" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B33&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="25" t="n">
         <f aca="false">IFERROR(D33/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.21875</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D34" s="25" t="n">
+      <c r="A34" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D34" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B34&amp;"*")</f>
         <v>11</v>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E34" s="25" t="n">
         <f aca="false">IFERROR(D34/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.34375</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D35" s="25" t="n">
+      <c r="A35" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D35" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B35&amp;"*")</f>
         <v>13</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="25" t="n">
         <f aca="false">IFERROR(D35/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.40625</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D36" s="25" t="n">
+      <c r="A36" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D36" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B36&amp;"*")</f>
         <v>5</v>
       </c>
-      <c r="E36" s="26" t="n">
+      <c r="E36" s="25" t="n">
         <f aca="false">IFERROR(D36/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.15625</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D37" s="25" t="n">
+      <c r="A37" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D37" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B37&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="25" t="n">
         <f aca="false">IFERROR(D37/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.21875</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D38" s="25" t="n">
+      <c r="A38" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D38" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B38&amp;"*")</f>
         <v>6</v>
       </c>
-      <c r="E38" s="26" t="n">
+      <c r="E38" s="25" t="n">
         <f aca="false">IFERROR(D38/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B39" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D39" s="25" t="n">
+      <c r="C39" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D39" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B39&amp;"*")</f>
         <v>15</v>
       </c>
-      <c r="E39" s="26" t="n">
+      <c r="E39" s="25" t="n">
         <f aca="false">IFERROR(D39/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.46875</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D40" s="25" t="n">
+      <c r="A40" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D40" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B40&amp;"*")</f>
         <v>7</v>
       </c>
-      <c r="E40" s="26" t="n">
+      <c r="E40" s="25" t="n">
         <f aca="false">IFERROR(D40/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.21875</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="C41" s="24" t="s">
+      <c r="A41" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B41" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="C41" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D41" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B41&amp;"*")</f>
         <v>17</v>
       </c>
-      <c r="E41" s="26" t="n">
+      <c r="E41" s="25" t="n">
         <f aca="false">IFERROR(D41/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.53125</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B42" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D42" s="25" t="n">
+      <c r="A42" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D42" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B42&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="E42" s="26" t="n">
+      <c r="E42" s="25" t="n">
         <f aca="false">IFERROR(D42/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.0625</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D43" s="25" t="n">
+      <c r="A43" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D43" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B43&amp;"*")</f>
         <v>4</v>
       </c>
-      <c r="E43" s="26" t="n">
+      <c r="E43" s="25" t="n">
         <f aca="false">IFERROR(D43/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D44" s="25" t="n">
+      <c r="A44" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D44" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B44&amp;"*")</f>
         <v>9</v>
       </c>
-      <c r="E44" s="26" t="n">
+      <c r="E44" s="25" t="n">
         <f aca="false">IFERROR(D44/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
         <v>0.28125</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
+      <c r="A46" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4038,61 +3995,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>324</v>
+        <v>319</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>326</v>
+        <v>321</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>328</v>
+        <v>323</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>330</v>
+        <v>325</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>332</v>
+        <v>327</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>334</v>
+        <v>329</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4101,32 +4058,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>337</v>
+        <v>332</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>339</v>
+        <v>334</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>341</v>
+        <v>336</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4145,7 +4102,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -4160,203 +4117,191 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="B5" s="32" t="n">
+      <c r="A5" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" s="31" t="n">
         <f aca="false">COUNTA('Track Tags'!$B$5:$B$36)</f>
         <v>32</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="B6" s="32" t="n">
+      <c r="A6" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$H$5:$H$36,"&gt;0")</f>
         <v>32</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="B7" s="32" t="n">
+      <c r="A7" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$H$5:$H$36,0)</f>
         <v>0</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B8" s="31" t="n">
+        <f aca="false">SUM('Track Tags'!$H$5:$H$36)</f>
+        <v>396</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" s="32" t="n">
+        <f aca="false">IFERROR(B8/B6,0)</f>
+        <v>12.375</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="B8" s="32" t="n">
-        <f aca="false">SUM('Track Tags'!$H$5:$H$36)</f>
-        <v>397</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="B9" s="33" t="n">
-        <f aca="false">IFERROR(B8/B6,0)</f>
-        <v>12.40625</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Lyric book + workbook")</f>
         <v>21</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="32" t="n">
+      <c r="A11" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Lyric book only")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="B12" s="32" t="n">
-        <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Author-supplied lyrics")</f>
-        <v>1</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="B13" s="32" t="n">
+      <c r="A12" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="B12" s="31" t="n">
         <f aca="false">COUNTA('Tag Dictionary'!$B$5:$B$44)</f>
         <v>40</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="B14" s="32" t="n">
+      <c r="C12" s="10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13" s="31" t="n">
         <f aca="false">COUNTIF('Tag Dictionary'!$D$5:$D$44,"&gt;0")</f>
         <v>40</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>363</v>
+      <c r="C13" s="10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
-        <v>364</v>
+      <c r="A16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="31" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$C$5:$C$36)-LEN(SUBSTITUTE('Track Tags'!$C$5:$C$36,",","")))+((LEN('Track Tags'!$C$5:$C$36)&gt;0)*1))</f>
+        <v>91</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="32" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$C$5:$C$36)-LEN(SUBSTITUTE('Track Tags'!$C$5:$C$36,",","")))+((LEN('Track Tags'!$C$5:$C$36)&gt;0)*1))</f>
-        <v>92</v>
+      <c r="A17" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="31" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$D$5:$D$36)-LEN(SUBSTITUTE('Track Tags'!$D$5:$D$36,",","")))+((LEN('Track Tags'!$D$5:$D$36)&gt;0)*1))</f>
+        <v>91</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="32" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$D$5:$D$36)-LEN(SUBSTITUTE('Track Tags'!$D$5:$D$36,",","")))+((LEN('Track Tags'!$D$5:$D$36)&gt;0)*1))</f>
-        <v>91</v>
+        <v>44</v>
+      </c>
+      <c r="B18" s="31" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$E$5:$E$36)-LEN(SUBSTITUTE('Track Tags'!$E$5:$E$36,",","")))+((LEN('Track Tags'!$E$5:$E$36)&gt;0)*1))</f>
+        <v>59</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="32" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$E$5:$E$36)-LEN(SUBSTITUTE('Track Tags'!$E$5:$E$36,",","")))+((LEN('Track Tags'!$E$5:$E$36)&gt;0)*1))</f>
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="B19" s="31" t="n">
+        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$F$5:$F$36)-LEN(SUBSTITUTE('Track Tags'!$F$5:$F$36,",","")))+((LEN('Track Tags'!$F$5:$F$36)&gt;0)*1))</f>
+        <v>88</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="32" t="n">
-        <f aca="false">SUMPRODUCT((LEN('Track Tags'!$F$5:$F$36)-LEN(SUBSTITUTE('Track Tags'!$F$5:$F$36,",","")))+((LEN('Track Tags'!$F$5:$F$36)&gt;0)*1))</f>
-        <v>88</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="B20" s="31" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$G$5:$G$36)-LEN(SUBSTITUTE('Track Tags'!$G$5:$G$36,",","")))+((LEN('Track Tags'!$G$5:$G$36)&gt;0)*1))</f>
         <v>67</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>369</v>
+      <c r="C20" s="10" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/docs/act-three-alchemizr-tags.xlsx
+++ b/docs/act-three-alchemizr-tags.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="368">
   <si>
     <t xml:space="preserve">The Matrx Alchemizr — Act III Tag Assignment</t>
   </si>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Primary</t>
   </si>
   <si>
-    <t xml:space="preserve">ActThreeReclamationLyrics.docx — the master lyric book. 32 tracks, whose order and titles match the live public.tracks roster exactly.</t>
+    <t xml:space="preserve">ActThreeReclamationLyrics.docx — the master lyric book. 32 tracks, whose order and titles match the live public.tracks roster exactly. Body Jumper prints a placeholder line there; its lyrics were supplied separately and read under the same test as every other track.</t>
   </si>
   <si>
     <t xml:space="preserve">Corroborating</t>
@@ -137,7 +137,13 @@
     <t xml:space="preserve">Tag counts</t>
   </si>
   <si>
-    <t xml:space="preserve">Roughly 2-3 tags per category per track, applied uniformly. Fewer tags make a track easier to score 100% on; more tags dilute each one. Nothing in the sources fixes this number.</t>
+    <t xml:space="preserve">There is no cap and no quota. A label goes on a track when the lyrics substantially evidence it, so counts run from one to four per category because the songs differ. No track is trimmed to match another, and none is padded to fill a column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every track is judged by the same test, whatever its length, position or source. Tags are the only thing allowed to differ between tracks, and they differ because the lyrics do.</t>
   </si>
   <si>
     <t xml:space="preserve">Track Tags — Act III "Reclamation"</t>
@@ -188,600 +194,606 @@
     <t xml:space="preserve">Release, Transform, Heartbreak</t>
   </si>
   <si>
+    <t xml:space="preserve">Fire, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Legacy, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyric book + workbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiation Through Fire | Invocation + Awakening | emberCore/ceremonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stolen authorship and betrayal turned into ignition: "thank you for the fire / I didn't know I needed it to rise"; "I'm taking back my authorship now". Polarity for the betrayal-to-rise inversion, Frequency for "feeding her my frequency". Air alongside Fire for the signal-and-record spine — "set the record straight", "I coded every note", "profiting off the signal".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reclamation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Gritty, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Transform, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, Earth, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, Power, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resonance, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Reclamation | Resurrection + Reclamation | goldenSignal/ceremonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrongful confinement and return: "fifty days ticking", "this is reclamation, the day Musiq Matrix came back". Earth for the cage/box, Resonance for "my voice is the code", Polarity for "the bigger the cage, the louder the call". Air because the voice is the song's named weapon — "they fear your voice / it's the weapon they can't confiscate".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Know Your Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Hypnotic, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus, Protect, Awaken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air, Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative Manipulation | Exposure + Warning | buriedTruth/tectonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold forensic naming: "I logged the tremors before the quake was admitted", "domino logic listen, then swing". Air for "every signal hums through the wires", Earth for cold-storage archive (workbook: buriedTruth/tectonic).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold On Through The Burial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Gritty, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal, Inspire, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth, Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhythm, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hope Against Collapse | Lament + Alignment | deepMemoryVault/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endurance anthem: "the same dirt meant to bury you can raise you up again". Earth for burial/ground, Water for "the rain came down like judgment" (workbook motion: ripple). Rhythm for the night-to-dawn cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chosen Ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethereal, Hypnotic, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Inspire, Connect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, Rebirth, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency, Resonance, Mentalism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective Awakening | Awakening + Alignment | goldenSignal/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation-breach awakening: "you cracked the first encryption they installed inside your brain", "a frequency for seekers". Mentalism for the installed-encryption framing, Air for lattices of lightning/broadcast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete Warnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protect, Awaken, Educate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loyalty, War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Rhythm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyric book only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street prophecy warning a friend about betrayers in his own ranks: "the concrete's got ears". Earth for concrete/paved-over ground, Cause &amp; Effect and Rhythm for "history repeats, a pattern etched in pain". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjacent (Reroute It)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Educate, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, Power, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authority Restoration | Override + Invocation | redSignalStorm/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gatekeeping answered by routing around it: "No seat? I'm building the table around it". Educate for the Les Paul / tape-loop history lesson; Cause &amp; Effect for "every era repeats the same tired design".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art! Official!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euphoric, Empowering, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Educate, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air, Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy, Faith, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency, Correspondence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI defended as sacred craft: "I plug into the cosmos, download divine semantics", "prophetic frequencies". Correspondence for "where circuitry meets soul / divine by design". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thought Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypnotic, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Awaken, Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentalism, Correspondence, Cause &amp; Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal Transmission | Invocation + Alignment | orbitalMind/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The album's explicit Mentalism lecture: "The first Hermetic principle is not love... It is Mind"; "As above, so below was never just a phrase"; "You are the code beneath the cause" (workbook skin: orbitalMind).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remember the Price (When You Speak the Name)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Transform, Inspire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy, Rebirth, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow work priced out loud: "I audited the dark", "I metabolized hell so you could access the best", "just remember the price when you speak the name". Fire for the torch handed forward. Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint of the Divine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethereal, Euphoric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Educate, Connect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correspondence, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divine Remembering | Invocation + Command Sequence | celestialGrid/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four-movement prayer pattern "written before time, stitched into the design"; "how the signal travels, how the frequency finds home". Correspondence for the inherited-pattern structure (workbook: celestialGrid).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flip It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Hypnotic, Euphoric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform, Heal, Educate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebirth, Freedom, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Mentalism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The album's purest Polarity track — the mechanic is literal reversal: "E-V-I-L L-I-V-E", "stressed" to "desserts", "the wound is where the gift begins", "the difference is the direction that you choose to read". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Am the Signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empowering, Hypnotic, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Focus, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, Freedom, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency, Resonance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"I am the signal / I am the frequency / I am the sound"; "coherence is the warfare"; "incoherent energy can't find a match"; "frequency is the protection". Earth for "built underground... channel it through the ground". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Create as I Speak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euphoric, Empowering, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifest, Inspire, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentalism, Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher Self Activation | Command Sequence + Momentum Surge | goldenSignal/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoken-word manifestation: "Each line is a law. I create as I speak"; "Abracadabra, I act like it's done". Mentalism for speech-as-cause; Frequency for "innovation ain't just sound, it's a frequency streak".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As Above, So Below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty, Hypnotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Educate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Faith, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correspondence, Polarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal Transmission | Alignment + Invocation | celestialGrid/orbital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correspondence is the title and the thesis; Polarity for the sustained heaven/hell inversion: "I seen Heaven in a cell and Hell in a mansion", "One mind... two wars". Earth for "thrones in the trenches".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elemental Orchestra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal, Connect, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Legacy, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, Resonance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotional Resurrection | Emotional Archive + Ascension | deepMemoryVault/ceremonial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asking to be witnessed, then becoming the witness: "I didn't need a crown. I needed a witness"; "You do not wait for flowers. You are the bloom." Gender for that self-generative turn — the Kybalion principle of the generative force acting within one being (workbook particles: lightFilaments + waterDroplets).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Witness Don’t Talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypnotic, Ethereal, Chill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awaken, Educate, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal Transmission | Awakening + Command Sequence | deepMemoryVault/hypnotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The observer self as recording architecture: "The Witness don't talk it transmits"; "you just finally found the frequency it sits". Workbook motion style is literally "hypnotic"; skin is deepMemoryVault (archive = Legacy).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonic Schemes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Nostalgic, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Heal, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Loyalty, War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarity, Cause &amp; Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacred Memory | Memory Echo + Purification | bureaucraticInferno/volatile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A bond corrupted by third-party influence, held open anyway: "still trying to hold a space for your redemption arc"; "even demons bend when faced with light". Polarity for that light/dark hinge; Water for the sustained grief.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Through the Fog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Dreamy, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Protect, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Loyalty, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longing | Memory Echo + Lament | submergedSignal/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love held behind a boundary: "I love you... but safety's the altar my soul answers to"; "a lighthouse still burning long after the storm". Water is unambiguous — fog, flood, waves, mist (workbook: submergedSignal/ripple).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gritty, Nostalgic, Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loyalty, Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrepaid loyalty demanded back: "Where the hell are my flowers? / For the nights I held your soul power". Rhythm for the month-by-month calendar close ("September, you left / October came in cold"). Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misguided Priorities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Gritty, Nostalgic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Protect, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, War, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grief Processing | Reflection + Lament | liquidMirror/ripple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grief redirected at the other's fate: "My grief ain't for myself now, it's for your soul alone"; "I can see the price you'll pay for gambling with your soul". Freedom for "all my fucking sovereignty" (workbook: liquidMirror/ripple/waterDroplets confirms Water).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hierophant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Awaken, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power, War, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Mentalism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritual War | Reflection + Awakening | liquidMirror/hypnotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">States the principle outright: "This isn't a curse it's cause and effect, a shadow that forms where light gets neglect"; "the Ten of Swords sits lodged in his spine". Mentalism for "the voice that his conscience designed".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foolish Pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Dark, Ethereal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbreak, Heal, Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Loyalty, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withholding as self-inflicted ruin: "You built an altar to withholding"; "the lessons that protected you became the bars you couldn't see". Earth and Rhythm for "the grave grows flowers too, long after the ground above goes still". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where the Phantom Fell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Ethereal, Nostalgic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cautionary elegy: "mercy needs choosing and love needs belief / and he traded them both for the crown of a thief"; "don't follow the path where the phantom fell". Polarity for "mistook his own heaven for hell". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Whole Cost of You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostalgic, Dreamy, Chill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Heal, Heartbreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Rebirth, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, Rhythm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure by burying an invented version of someone: "I know I wrote him myself, line after line in red". Gender for that generative projection — a figure authored inside the self; Rhythm for "the tower falls so the tower can be free". Fire for "let it go up like smoke, let it go up like a flame". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Without Stains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protect, Release, Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power, Faith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truth Broadcast | Confession + Transmutation | crucibleEngine/volatile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A staged ritual ambush survived: "They wanted blood without stains"; "You can't drain a soul that was never yours to claim". Fire from the workbook crucibleEngine/ash/burningPaper treatment; Earth for the body as vessel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slumlord Fundamentalists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gritty, Dark, Empowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Freedom, Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institutional Corruption | Exposure + Indictment | bureaucraticInferno/militant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentary indictment of housing corruption: "constructive eviction", "welfare fraud", "every empire crumbles, that's the fatal flaw". Earth alone — the whole song is buildings, locks, heat and habitable space. Rhythm for the September-to-February sequence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reckoning Already Rolled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark, Empowering, Gritty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus, Protect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power, Freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consequence stated as already-completed: "The reckoning isn't incoming / the reckoning already rolled". Mentalism for "I sharpen clarity like a scalpel / I don't chase you; I undo you". Lyric book only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architect of the Aftermath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educate, Protect, Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earth, Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War, Power, Legacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cause &amp; Effect, Correspondence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Sovereignty | Alignment + Transmutation | celestialGrid/tectonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forensic account of an illegal eviction: "I am the Architect of the Aftermath / mapping fault lines in your rigged collapse"; "the blueprint indicts your method in the light". Correspondence for blueprint-mirrors-territory (workbook motion: tectonic confirms Earth).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seer Broke Chains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release, Protect, Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire, Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freedom, War, Rebirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritual War | Revolt + Transmutation | containmentFailure/volatile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curse reversed on its sender: "I sabotage, reverse the code"; "now every curse turns back to me"; "I walked through fire, I broke your chains". Water for "the sea returns where fire once flowed".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire in My Veins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform, Manifest, Inspire</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fire</t>
   </si>
   <si>
-    <t xml:space="preserve">Power, Legacy, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polarity, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyric book + workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initiation Through Fire | Invocation + Awakening | emberCore/ceremonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stolen authorship and betrayal turned into ignition: "thank you for the fire / I didn't know I needed it to rise"; "I'm taking back my authorship now". Polarity for the betrayal-to-rise inversion, Frequency for "feeding her my frequency".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reclamation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Gritty, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Transform, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire, Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, Power, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resonance, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Reclamation | Resurrection + Reclamation | goldenSignal/ceremonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrongful confinement and return: "fifty days ticking", "this is reclamation, the day Musiq Matrix came back". Earth for the cage/box, Resonance for "my voice is the code", Polarity for "the bigger the cage, the louder the call".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Know Your Names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Hypnotic, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focus, Protect, Awaken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air, Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative Manipulation | Exposure + Warning | buriedTruth/tectonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cold forensic naming: "I logged the tremors before the quake was admitted", "domino logic listen, then swing". Air for "every signal hums through the wires", Earth for cold-storage archive (workbook: buriedTruth/tectonic).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hold On Through The Burial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Gritty, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heal, Inspire, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth, Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhythm, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hope Against Collapse | Lament + Alignment | deepMemoryVault/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endurance anthem: "the same dirt meant to bury you can raise you up again". Earth for burial/ground, Water for "the rain came down like judgment" (workbook motion: ripple). Rhythm for the night-to-dawn cycle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chosen Ones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethereal, Hypnotic, Empowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Inspire, Connect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, Rebirth, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency, Resonance, Mentalism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collective Awakening | Awakening + Alignment | goldenSignal/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation-breach awakening: "you cracked the first encryption they installed inside your brain", "a frequency for seekers". Mentalism for the installed-encryption framing, Air for lattices of lightning/broadcast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete Warnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protect, Awaken, Educate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth, Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loyalty, War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Rhythm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyric book only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street prophecy warning a friend about betrayers in his own ranks: "the concrete's got ears". Earth for concrete/paved-over ground, Cause &amp; Effect and Rhythm for "history repeats, a pattern etched in pain". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjacent (Reroute It)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Educate, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, Power, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authority Restoration | Override + Invocation | redSignalStorm/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gatekeeping answered by routing around it: "No seat? I'm building the table around it". Educate for the Les Paul / tape-loop history lesson; Cause &amp; Effect for "every era repeats the same tired design".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art! Official!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euphoric, Empowering, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Educate, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air, Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy, Faith, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency, Correspondence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI defended as sacred craft: "I plug into the cosmos, download divine semantics", "prophetic frequencies". Correspondence for "where circuitry meets soul / divine by design". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thought Form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypnotic, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Awaken, Transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentalism, Correspondence, Cause &amp; Effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal Transmission | Invocation + Alignment | orbitalMind/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The album's explicit Mentalism lecture: "The first Hermetic principle is not love... It is Mind"; "As above, so below was never just a phrase"; "You are the code beneath the cause" (workbook skin: orbitalMind).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remember the Price (When You Speak the Name)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty, Empowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Transform, Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy, Rebirth, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow work priced out loud: "I audited the dark", "I metabolized hell so you could access the best", "just remember the price when you speak the name". Fire for the torch handed forward. Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint of the Divine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethereal, Euphoric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Educate, Connect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondence, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divine Remembering | Invocation + Command Sequence | celestialGrid/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four-movement prayer pattern "written before time, stitched into the design"; "how the signal travels, how the frequency finds home". Correspondence for the inherited-pattern structure (workbook: celestialGrid).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flip It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Hypnotic, Euphoric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform, Heal, Educate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth, Freedom, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polarity, Mentalism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The album's purest Polarity track — the mechanic is literal reversal: "E-V-I-L L-I-V-E", "stressed" to "desserts", "the wound is where the gift begins", "the difference is the direction that you choose to read". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Am the Signal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empowering, Hypnotic, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Focus, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, Freedom, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency, Resonance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"I am the signal / I am the frequency / I am the sound"; "coherence is the warfare"; "incoherent energy can't find a match"; "frequency is the protection". Earth for "built underground... channel it through the ground". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Create as I Speak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euphoric, Empowering, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifest, Inspire, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentalism, Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higher Self Activation | Command Sequence + Momentum Surge | goldenSignal/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spoken-word manifestation: "Each line is a law. I create as I speak"; "Abracadabra, I act like it's done". Mentalism for speech-as-cause; Frequency for "innovation ain't just sound, it's a frequency streak".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As Above, So Below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty, Hypnotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Educate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Faith, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondence, Polarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal Transmission | Alignment + Invocation | celestialGrid/orbital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondence is the title and the thesis; Polarity for the sustained heaven/hell inversion: "I seen Heaven in a cell and Hell in a mansion", "One mind... two wars". Earth for "thrones in the trenches".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elemental Orchestra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heal, Connect, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water, Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Legacy, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender, Resonance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emotional Resurrection | Emotional Archive + Ascension | deepMemoryVault/ceremonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asking to be witnessed, then becoming the witness: "I didn't need a crown. I needed a witness"; "You do not wait for flowers. You are the bloom." Gender for that self-generative turn — the Kybalion principle of the generative force acting within one being (workbook particles: lightFilaments + waterDroplets).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Witness Don’t Talk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypnotic, Ethereal, Chill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awaken, Educate, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legacy, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal Transmission | Awakening + Command Sequence | deepMemoryVault/hypnotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The observer self as recording architecture: "The Witness don't talk it transmits"; "you just finally found the frequency it sits". Workbook motion style is literally "hypnotic"; skin is deepMemoryVault (archive = Legacy).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonic Schemes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Nostalgic, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Heal, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water, Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Loyalty, War</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polarity, Cause &amp; Effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sacred Memory | Memory Echo + Purification | bureaucraticInferno/volatile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A bond corrupted by third-party influence, held open anyway: "still trying to hold a space for your redemption arc"; "even demons bend when faced with light". Polarity for that light/dark hinge; Water for the sustained grief.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Through the Fog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Dreamy, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Protect, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water, Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Loyalty, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longing | Memory Echo + Lament | submergedSignal/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love held behind a boundary: "I love you... but safety's the altar my soul answers to"; "a lighthouse still burning long after the storm". Water is unambiguous — fog, flood, waves, mist (workbook: submergedSignal/ripple).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flowers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gritty, Nostalgic, Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loyalty, Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unrepaid loyalty demanded back: "Where the hell are my flowers? / For the nights I held your soul power". Rhythm for the month-by-month calendar close ("September, you left / October came in cold"). Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Misguided Priorities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Gritty, Nostalgic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Protect, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, War, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grief Processing | Reflection + Lament | liquidMirror/ripple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grief redirected at the other's fate: "My grief ain't for myself now, it's for your soul alone"; "I can see the price you'll pay for gambling with your soul". Freedom for "all my fucking sovereignty" (workbook: liquidMirror/ripple/waterDroplets confirms Water).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hierophant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Awaken, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power, War, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Mentalism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiritual War | Reflection + Awakening | liquidMirror/hypnotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States the principle outright: "This isn't a curse it's cause and effect, a shadow that forms where light gets neglect"; "the Ten of Swords sits lodged in his spine". Mentalism for "the voice that his conscience designed".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foolish Pride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Dark, Ethereal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heartbreak, Heal, Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Loyalty, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withholding as self-inflicted ruin: "You built an altar to withholding"; "the lessons that protected you became the bars you couldn't see". Earth and Rhythm for "the grave grows flowers too, long after the ground above goes still". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where the Phantom Fell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Ethereal, Nostalgic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faith, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A cautionary elegy: "mercy needs choosing and love needs belief / and he traded them both for the crown of a thief"; "don't follow the path where the phantom fell". Polarity for "mistook his own heaven for hell". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Whole Cost of You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nostalgic, Dreamy, Chill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Heal, Heartbreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love, Rebirth, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender, Rhythm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closure by burying an invented version of someone: "I know I wrote him myself, line after line in red". Gender for that generative projection — a figure authored inside the self; Rhythm for "the tower falls so the tower can be free". Fire for "let it go up like smoke, let it go up like a flame". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood Without Stains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protect, Release, Transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power, Faith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truth Broadcast | Confession + Transmutation | crucibleEngine/volatile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A staged ritual ambush survived: "They wanted blood without stains"; "You can't drain a soul that was never yours to claim". Fire from the workbook crucibleEngine/ash/burningPaper treatment; Earth for the body as vessel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slumlord Fundamentalists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gritty, Dark, Empowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Freedom, Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institutional Corruption | Exposure + Indictment | bureaucraticInferno/militant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentary indictment of housing corruption: "constructive eviction", "welfare fraud", "every empire crumbles, that's the fatal flaw". Earth alone — the whole song is buildings, locks, heat and habitable space. Rhythm for the September-to-February sequence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reckoning Already Rolled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark, Empowering, Gritty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focus, Protect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power, Freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consequence stated as already-completed: "The reckoning isn't incoming / the reckoning already rolled". Mentalism for "I sharpen clarity like a scalpel / I don't chase you; I undo you". Lyric book only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architect of the Aftermath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educate, Protect, Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earth, Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">War, Power, Legacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause &amp; Effect, Correspondence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal Sovereignty | Alignment + Transmutation | celestialGrid/tectonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forensic account of an illegal eviction: "I am the Architect of the Aftermath / mapping fault lines in your rigged collapse"; "the blueprint indicts your method in the light". Correspondence for blueprint-mirrors-territory (workbook motion: tectonic confirms Earth).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seer Broke Chains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release, Protect, Transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire, Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freedom, War, Rebirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiritual War | Revolt + Transmutation | containmentFailure/volatile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curse reversed on its sender: "I sabotage, reverse the code"; "now every curse turns back to me"; "I walked through fire, I broke your chains". Water for "the sea returns where fire once flowed".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire in My Veins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform, Manifest, Inspire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Power, Rebirth, Legacy</t>
   </si>
   <si>
@@ -794,25 +806,22 @@
     <t xml:space="preserve">Body Jumper</t>
   </si>
   <si>
-    <t xml:space="preserve">Dark, Hypnotic, Empowering</t>
+    <t xml:space="preserve">Dark, Hypnotic, Ethereal, Empowering</t>
   </si>
   <si>
     <t xml:space="preserve">Release, Transform, Protect</t>
   </si>
   <si>
-    <t xml:space="preserve">Fire, Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebirth, Power, Freedom</t>
+    <t xml:space="preserve">Rebirth, Power, Legacy, Freedom</t>
   </si>
   <si>
     <t xml:space="preserve">Polarity, Correspondence, Cause &amp; Effect</t>
   </si>
   <si>
-    <t xml:space="preserve">Possession refused, then integrated: "I am not a host—I deny access"; "I am the axis at the gate" give Protect; the repeated "Leave every borrowed voice / name / version" and "set my old self ablaze" give Release; "I walk out burned—But redesigned" gives Transform and Rebirth. Elements are named outright in the outro — "Fire refined. Now air defines." Correspondence for "The war was never outside me—it just wore a borrowed face / Every mimic that I banished was a mirror of my case"; Polarity for "I dissolve the last distinction between hunted and the hunter"; Cause &amp; Effect for "You don't disrupt the process—you become the documentation". Freedom for "walking through ungated doors" and the explicit end of the war; Power for melting the throne "down to the gold it was always structured under".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag columns C:G are the editable cells. Labels must match the Tag Dictionary sheet exactly; the database seed rejects anything else. Body Jumper is intentionally blank — no lyrics exist in any supplied source.</t>
+    <t xml:space="preserve">Possession refused, then integrated: "I am not a host—I deny access"; "I am the axis at the gate" give Protect; the repeated "Leave every borrowed voice / name / version" and "set my old self ablaze" give Release; "I walk out burned—But redesigned" gives Transform and Rebirth. Elements are named outright in the outro — "Fire refined. Now air defines." Correspondence for "The war was never outside me—it just wore a borrowed face / Every mimic that I banished was a mirror of my case"; Polarity for "I dissolve the last distinction between hunted and the hunter"; Cause &amp; Effect for "You don't disrupt the process—you become the documentation". Freedom for "walking through ungated doors" and the explicit end of the war; Power for melting the throne "down to the gold it was always structured under"; Legacy for the permanent-record motif that recurs five times — "a permanent speech", "you become the documentation", "engraved into the stone", "a platinum-level record", "a documented trail". Ethereal alongside Dark and Hypnotic because the forensic verses and the Crucible Code ascension are two modes the track actually holds. War is deliberately absent: the lyric ends it outright — "no more enemy to name, no more armor, no more war".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag columns C:G are the editable cells. Labels must match the Tag Dictionary sheet exactly; the database seed rejects anything else. Counts vary by track because the evidence does — no row is trimmed to match another or padded to fill a column.</t>
   </si>
   <si>
     <t xml:space="preserve">The closed vocabulary seeded into public.tag_dictionary. Usage counts read live from Track Tags.</t>
@@ -1688,7 +1697,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1871,6 +1880,14 @@
       </c>
       <c r="B27" s="4" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1906,119 +1923,119 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">IF(C5="",0,LEN(C5)-LEN(SUBSTITUTE(C5,",",""))+1)+IF(D5="",0,LEN(D5)-LEN(SUBSTITUTE(D5,",",""))+1)+IF(E5="",0,LEN(E5)-LEN(SUBSTITUTE(E5,",",""))+1)+IF(F5="",0,LEN(F5)-LEN(SUBSTITUTE(F5,",",""))+1)+IF(G5="",0,LEN(G5)-LEN(SUBSTITUTE(G5,",",""))+1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">IF(C6="",0,LEN(C6)-LEN(SUBSTITUTE(C6,",",""))+1)+IF(D6="",0,LEN(D6)-LEN(SUBSTITUTE(D6,",",""))+1)+IF(E6="",0,LEN(E6)-LEN(SUBSTITUTE(E6,",",""))+1)+IF(F6="",0,LEN(F6)-LEN(SUBSTITUTE(F6,",",""))+1)+IF(G6="",0,LEN(G6)-LEN(SUBSTITUTE(G6,",",""))+1)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2026,35 +2043,35 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="false">IF(C7="",0,LEN(C7)-LEN(SUBSTITUTE(C7,",",""))+1)+IF(D7="",0,LEN(D7)-LEN(SUBSTITUTE(D7,",",""))+1)+IF(E7="",0,LEN(E7)-LEN(SUBSTITUTE(E7,",",""))+1)+IF(F7="",0,LEN(F7)-LEN(SUBSTITUTE(F7,",",""))+1)+IF(G7="",0,LEN(G7)-LEN(SUBSTITUTE(G7,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2062,35 +2079,35 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">IF(C8="",0,LEN(C8)-LEN(SUBSTITUTE(C8,",",""))+1)+IF(D8="",0,LEN(D8)-LEN(SUBSTITUTE(D8,",",""))+1)+IF(E8="",0,LEN(E8)-LEN(SUBSTITUTE(E8,",",""))+1)+IF(F8="",0,LEN(F8)-LEN(SUBSTITUTE(F8,",",""))+1)+IF(G8="",0,LEN(G8)-LEN(SUBSTITUTE(G8,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2098,35 +2115,35 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">IF(C9="",0,LEN(C9)-LEN(SUBSTITUTE(C9,",",""))+1)+IF(D9="",0,LEN(D9)-LEN(SUBSTITUTE(D9,",",""))+1)+IF(E9="",0,LEN(E9)-LEN(SUBSTITUTE(E9,",",""))+1)+IF(F9="",0,LEN(F9)-LEN(SUBSTITUTE(F9,",",""))+1)+IF(G9="",0,LEN(G9)-LEN(SUBSTITUTE(G9,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2134,35 +2151,35 @@
         <v>6</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">IF(C10="",0,LEN(C10)-LEN(SUBSTITUTE(C10,",",""))+1)+IF(D10="",0,LEN(D10)-LEN(SUBSTITUTE(D10,",",""))+1)+IF(E10="",0,LEN(E10)-LEN(SUBSTITUTE(E10,",",""))+1)+IF(F10="",0,LEN(F10)-LEN(SUBSTITUTE(F10,",",""))+1)+IF(G10="",0,LEN(G10)-LEN(SUBSTITUTE(G10,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2170,35 +2187,35 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H11" s="16" t="n">
         <f aca="false">IF(C11="",0,LEN(C11)-LEN(SUBSTITUTE(C11,",",""))+1)+IF(D11="",0,LEN(D11)-LEN(SUBSTITUTE(D11,",",""))+1)+IF(E11="",0,LEN(E11)-LEN(SUBSTITUTE(E11,",",""))+1)+IF(F11="",0,LEN(F11)-LEN(SUBSTITUTE(F11,",",""))+1)+IF(G11="",0,LEN(G11)-LEN(SUBSTITUTE(G11,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2206,35 +2223,35 @@
         <v>8</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">IF(C12="",0,LEN(C12)-LEN(SUBSTITUTE(C12,",",""))+1)+IF(D12="",0,LEN(D12)-LEN(SUBSTITUTE(D12,",",""))+1)+IF(E12="",0,LEN(E12)-LEN(SUBSTITUTE(E12,",",""))+1)+IF(F12="",0,LEN(F12)-LEN(SUBSTITUTE(F12,",",""))+1)+IF(G12="",0,LEN(G12)-LEN(SUBSTITUTE(G12,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2242,35 +2259,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false">IF(C13="",0,LEN(C13)-LEN(SUBSTITUTE(C13,",",""))+1)+IF(D13="",0,LEN(D13)-LEN(SUBSTITUTE(D13,",",""))+1)+IF(E13="",0,LEN(E13)-LEN(SUBSTITUTE(E13,",",""))+1)+IF(F13="",0,LEN(F13)-LEN(SUBSTITUTE(F13,",",""))+1)+IF(G13="",0,LEN(G13)-LEN(SUBSTITUTE(G13,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2278,35 +2295,35 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">IF(C14="",0,LEN(C14)-LEN(SUBSTITUTE(C14,",",""))+1)+IF(D14="",0,LEN(D14)-LEN(SUBSTITUTE(D14,",",""))+1)+IF(E14="",0,LEN(E14)-LEN(SUBSTITUTE(E14,",",""))+1)+IF(F14="",0,LEN(F14)-LEN(SUBSTITUTE(F14,",",""))+1)+IF(G14="",0,LEN(G14)-LEN(SUBSTITUTE(G14,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2314,35 +2331,35 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H15" s="16" t="n">
         <f aca="false">IF(C15="",0,LEN(C15)-LEN(SUBSTITUTE(C15,",",""))+1)+IF(D15="",0,LEN(D15)-LEN(SUBSTITUTE(D15,",",""))+1)+IF(E15="",0,LEN(E15)-LEN(SUBSTITUTE(E15,",",""))+1)+IF(F15="",0,LEN(F15)-LEN(SUBSTITUTE(F15,",",""))+1)+IF(G15="",0,LEN(G15)-LEN(SUBSTITUTE(G15,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2350,35 +2367,35 @@
         <v>12</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">IF(C16="",0,LEN(C16)-LEN(SUBSTITUTE(C16,",",""))+1)+IF(D16="",0,LEN(D16)-LEN(SUBSTITUTE(D16,",",""))+1)+IF(E16="",0,LEN(E16)-LEN(SUBSTITUTE(E16,",",""))+1)+IF(F16="",0,LEN(F16)-LEN(SUBSTITUTE(F16,",",""))+1)+IF(G16="",0,LEN(G16)-LEN(SUBSTITUTE(G16,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2386,35 +2403,35 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">IF(C17="",0,LEN(C17)-LEN(SUBSTITUTE(C17,",",""))+1)+IF(D17="",0,LEN(D17)-LEN(SUBSTITUTE(D17,",",""))+1)+IF(E17="",0,LEN(E17)-LEN(SUBSTITUTE(E17,",",""))+1)+IF(F17="",0,LEN(F17)-LEN(SUBSTITUTE(F17,",",""))+1)+IF(G17="",0,LEN(G17)-LEN(SUBSTITUTE(G17,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2422,35 +2439,35 @@
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IF(C18="",0,LEN(C18)-LEN(SUBSTITUTE(C18,",",""))+1)+IF(D18="",0,LEN(D18)-LEN(SUBSTITUTE(D18,",",""))+1)+IF(E18="",0,LEN(E18)-LEN(SUBSTITUTE(E18,",",""))+1)+IF(F18="",0,LEN(F18)-LEN(SUBSTITUTE(F18,",",""))+1)+IF(G18="",0,LEN(G18)-LEN(SUBSTITUTE(G18,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2458,35 +2475,35 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H19" s="16" t="n">
         <f aca="false">IF(C19="",0,LEN(C19)-LEN(SUBSTITUTE(C19,",",""))+1)+IF(D19="",0,LEN(D19)-LEN(SUBSTITUTE(D19,",",""))+1)+IF(E19="",0,LEN(E19)-LEN(SUBSTITUTE(E19,",",""))+1)+IF(F19="",0,LEN(F19)-LEN(SUBSTITUTE(F19,",",""))+1)+IF(G19="",0,LEN(G19)-LEN(SUBSTITUTE(G19,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2494,35 +2511,35 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">IF(C20="",0,LEN(C20)-LEN(SUBSTITUTE(C20,",",""))+1)+IF(D20="",0,LEN(D20)-LEN(SUBSTITUTE(D20,",",""))+1)+IF(E20="",0,LEN(E20)-LEN(SUBSTITUTE(E20,",",""))+1)+IF(F20="",0,LEN(F20)-LEN(SUBSTITUTE(F20,",",""))+1)+IF(G20="",0,LEN(G20)-LEN(SUBSTITUTE(G20,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2530,35 +2547,35 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H21" s="16" t="n">
         <f aca="false">IF(C21="",0,LEN(C21)-LEN(SUBSTITUTE(C21,",",""))+1)+IF(D21="",0,LEN(D21)-LEN(SUBSTITUTE(D21,",",""))+1)+IF(E21="",0,LEN(E21)-LEN(SUBSTITUTE(E21,",",""))+1)+IF(F21="",0,LEN(F21)-LEN(SUBSTITUTE(F21,",",""))+1)+IF(G21="",0,LEN(G21)-LEN(SUBSTITUTE(G21,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2566,35 +2583,35 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">IF(C22="",0,LEN(C22)-LEN(SUBSTITUTE(C22,",",""))+1)+IF(D22="",0,LEN(D22)-LEN(SUBSTITUTE(D22,",",""))+1)+IF(E22="",0,LEN(E22)-LEN(SUBSTITUTE(E22,",",""))+1)+IF(F22="",0,LEN(F22)-LEN(SUBSTITUTE(F22,",",""))+1)+IF(G22="",0,LEN(G22)-LEN(SUBSTITUTE(G22,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2602,35 +2619,35 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">IF(C23="",0,LEN(C23)-LEN(SUBSTITUTE(C23,",",""))+1)+IF(D23="",0,LEN(D23)-LEN(SUBSTITUTE(D23,",",""))+1)+IF(E23="",0,LEN(E23)-LEN(SUBSTITUTE(E23,",",""))+1)+IF(F23="",0,LEN(F23)-LEN(SUBSTITUTE(F23,",",""))+1)+IF(G23="",0,LEN(G23)-LEN(SUBSTITUTE(G23,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2638,35 +2655,35 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H24" s="19" t="n">
         <f aca="false">IF(C24="",0,LEN(C24)-LEN(SUBSTITUTE(C24,",",""))+1)+IF(D24="",0,LEN(D24)-LEN(SUBSTITUTE(D24,",",""))+1)+IF(E24="",0,LEN(E24)-LEN(SUBSTITUTE(E24,",",""))+1)+IF(F24="",0,LEN(F24)-LEN(SUBSTITUTE(F24,",",""))+1)+IF(G24="",0,LEN(G24)-LEN(SUBSTITUTE(G24,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2674,35 +2691,35 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">IF(C25="",0,LEN(C25)-LEN(SUBSTITUTE(C25,",",""))+1)+IF(D25="",0,LEN(D25)-LEN(SUBSTITUTE(D25,",",""))+1)+IF(E25="",0,LEN(E25)-LEN(SUBSTITUTE(E25,",",""))+1)+IF(F25="",0,LEN(F25)-LEN(SUBSTITUTE(F25,",",""))+1)+IF(G25="",0,LEN(G25)-LEN(SUBSTITUTE(G25,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2710,35 +2727,35 @@
         <v>22</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H26" s="19" t="n">
         <f aca="false">IF(C26="",0,LEN(C26)-LEN(SUBSTITUTE(C26,",",""))+1)+IF(D26="",0,LEN(D26)-LEN(SUBSTITUTE(D26,",",""))+1)+IF(E26="",0,LEN(E26)-LEN(SUBSTITUTE(E26,",",""))+1)+IF(F26="",0,LEN(F26)-LEN(SUBSTITUTE(F26,",",""))+1)+IF(G26="",0,LEN(G26)-LEN(SUBSTITUTE(G26,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2746,35 +2763,35 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">IF(C27="",0,LEN(C27)-LEN(SUBSTITUTE(C27,",",""))+1)+IF(D27="",0,LEN(D27)-LEN(SUBSTITUTE(D27,",",""))+1)+IF(E27="",0,LEN(E27)-LEN(SUBSTITUTE(E27,",",""))+1)+IF(F27="",0,LEN(F27)-LEN(SUBSTITUTE(F27,",",""))+1)+IF(G27="",0,LEN(G27)-LEN(SUBSTITUTE(G27,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2782,35 +2799,35 @@
         <v>24</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H28" s="19" t="n">
         <f aca="false">IF(C28="",0,LEN(C28)-LEN(SUBSTITUTE(C28,",",""))+1)+IF(D28="",0,LEN(D28)-LEN(SUBSTITUTE(D28,",",""))+1)+IF(E28="",0,LEN(E28)-LEN(SUBSTITUTE(E28,",",""))+1)+IF(F28="",0,LEN(F28)-LEN(SUBSTITUTE(F28,",",""))+1)+IF(G28="",0,LEN(G28)-LEN(SUBSTITUTE(G28,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2818,35 +2835,35 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">IF(C29="",0,LEN(C29)-LEN(SUBSTITUTE(C29,",",""))+1)+IF(D29="",0,LEN(D29)-LEN(SUBSTITUTE(D29,",",""))+1)+IF(E29="",0,LEN(E29)-LEN(SUBSTITUTE(E29,",",""))+1)+IF(F29="",0,LEN(F29)-LEN(SUBSTITUTE(F29,",",""))+1)+IF(G29="",0,LEN(G29)-LEN(SUBSTITUTE(G29,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2854,35 +2871,35 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H30" s="19" t="n">
         <f aca="false">IF(C30="",0,LEN(C30)-LEN(SUBSTITUTE(C30,",",""))+1)+IF(D30="",0,LEN(D30)-LEN(SUBSTITUTE(D30,",",""))+1)+IF(E30="",0,LEN(E30)-LEN(SUBSTITUTE(E30,",",""))+1)+IF(F30="",0,LEN(F30)-LEN(SUBSTITUTE(F30,",",""))+1)+IF(G30="",0,LEN(G30)-LEN(SUBSTITUTE(G30,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2890,35 +2907,35 @@
         <v>27</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">IF(C31="",0,LEN(C31)-LEN(SUBSTITUTE(C31,",",""))+1)+IF(D31="",0,LEN(D31)-LEN(SUBSTITUTE(D31,",",""))+1)+IF(E31="",0,LEN(E31)-LEN(SUBSTITUTE(E31,",",""))+1)+IF(F31="",0,LEN(F31)-LEN(SUBSTITUTE(F31,",",""))+1)+IF(G31="",0,LEN(G31)-LEN(SUBSTITUTE(G31,",",""))+1)</f>
         <v>11</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2926,35 +2943,35 @@
         <v>28</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H32" s="19" t="n">
         <f aca="false">IF(C32="",0,LEN(C32)-LEN(SUBSTITUTE(C32,",",""))+1)+IF(D32="",0,LEN(D32)-LEN(SUBSTITUTE(D32,",",""))+1)+IF(E32="",0,LEN(E32)-LEN(SUBSTITUTE(E32,",",""))+1)+IF(F32="",0,LEN(F32)-LEN(SUBSTITUTE(F32,",",""))+1)+IF(G32="",0,LEN(G32)-LEN(SUBSTITUTE(G32,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2962,35 +2979,35 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H33" s="16" t="n">
         <f aca="false">IF(C33="",0,LEN(C33)-LEN(SUBSTITUTE(C33,",",""))+1)+IF(D33="",0,LEN(D33)-LEN(SUBSTITUTE(D33,",",""))+1)+IF(E33="",0,LEN(E33)-LEN(SUBSTITUTE(E33,",",""))+1)+IF(F33="",0,LEN(F33)-LEN(SUBSTITUTE(F33,",",""))+1)+IF(G33="",0,LEN(G33)-LEN(SUBSTITUTE(G33,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2998,35 +3015,35 @@
         <v>30</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H34" s="19" t="n">
         <f aca="false">IF(C34="",0,LEN(C34)-LEN(SUBSTITUTE(C34,",",""))+1)+IF(D34="",0,LEN(D34)-LEN(SUBSTITUTE(D34,",",""))+1)+IF(E34="",0,LEN(E34)-LEN(SUBSTITUTE(E34,",",""))+1)+IF(F34="",0,LEN(F34)-LEN(SUBSTITUTE(F34,",",""))+1)+IF(G34="",0,LEN(G34)-LEN(SUBSTITUTE(G34,",",""))+1)</f>
         <v>13</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3034,76 +3051,76 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>54</v>
+        <v>255</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H35" s="16" t="n">
         <f aca="false">IF(C35="",0,LEN(C35)-LEN(SUBSTITUTE(C35,",",""))+1)+IF(D35="",0,LEN(D35)-LEN(SUBSTITUTE(D35,",",""))+1)+IF(E35="",0,LEN(E35)-LEN(SUBSTITUTE(E35,",",""))+1)+IF(F35="",0,LEN(F35)-LEN(SUBSTITUTE(F35,",",""))+1)+IF(G35="",0,LEN(G35)-LEN(SUBSTITUTE(G35,",",""))+1)</f>
         <v>12</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>258</v>
+        <v>56</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H36" s="19" t="n">
         <f aca="false">IF(C36="",0,LEN(C36)-LEN(SUBSTITUTE(C36,",",""))+1)+IF(D36="",0,LEN(D36)-LEN(SUBSTITUTE(D36,",",""))+1)+IF(E36="",0,LEN(E36)-LEN(SUBSTITUTE(E36,",",""))+1)+IF(F36="",0,LEN(F36)-LEN(SUBSTITUTE(F36,",",""))+1)+IF(G36="",0,LEN(G36)-LEN(SUBSTITUTE(G36,",",""))+1)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -3173,35 +3190,35 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D5" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B5&amp;"*")</f>
@@ -3214,13 +3231,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D6" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B6&amp;"*")</f>
@@ -3233,13 +3250,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D7" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B7&amp;"*")</f>
@@ -3252,13 +3269,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B8" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>274</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>271</v>
       </c>
       <c r="D8" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B8&amp;"*")</f>
@@ -3271,13 +3288,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D9" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B9&amp;"*")</f>
@@ -3290,32 +3307,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B10&amp;"*")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">IFERROR(D10/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
-        <v>0.3125</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D11" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B11&amp;"*")</f>
@@ -3328,13 +3345,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D12" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B12&amp;"*")</f>
@@ -3347,13 +3364,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D13" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$C$5:$C$36,"*"&amp;B13&amp;"*")</f>
@@ -3366,13 +3383,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D14" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B14&amp;"*")</f>
@@ -3385,13 +3402,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B15&amp;"*")</f>
@@ -3404,13 +3421,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D16" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B16&amp;"*")</f>
@@ -3423,13 +3440,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B17" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>285</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>282</v>
       </c>
       <c r="D17" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B17&amp;"*")</f>
@@ -3442,13 +3459,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D18" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B18&amp;"*")</f>
@@ -3461,13 +3478,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D19" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B19&amp;"*")</f>
@@ -3480,13 +3497,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D20" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B20&amp;"*")</f>
@@ -3499,13 +3516,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D21" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B21&amp;"*")</f>
@@ -3518,13 +3535,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D22" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B22&amp;"*")</f>
@@ -3537,13 +3554,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D23" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B23&amp;"*")</f>
@@ -3556,13 +3573,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D24" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$D$5:$D$36,"*"&amp;B24&amp;"*")</f>
@@ -3575,13 +3592,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>54</v>
+        <v>255</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D25" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B25&amp;"*")</f>
@@ -3594,13 +3611,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D26" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B26&amp;"*")</f>
@@ -3613,32 +3630,32 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B27&amp;"*")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">IFERROR(D27/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
-        <v>0.46875</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D28" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$E$5:$E$36,"*"&amp;B28&amp;"*")</f>
@@ -3651,13 +3668,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B29&amp;"*")</f>
@@ -3670,13 +3687,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D30" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B30&amp;"*")</f>
@@ -3689,32 +3706,32 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D31" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B31&amp;"*")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" s="25" t="n">
         <f aca="false">IFERROR(D31/COUNTA('Track Tags'!$B$5:$B$36),0)</f>
-        <v>0.34375</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B32" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="23" t="s">
         <v>301</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>298</v>
       </c>
       <c r="D32" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B32&amp;"*")</f>
@@ -3727,13 +3744,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D33" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B33&amp;"*")</f>
@@ -3746,13 +3763,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D34" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B34&amp;"*")</f>
@@ -3765,13 +3782,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B35&amp;"*")</f>
@@ -3784,13 +3801,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D36" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$F$5:$F$36,"*"&amp;B36&amp;"*")</f>
@@ -3803,13 +3820,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D37" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B37&amp;"*")</f>
@@ -3822,13 +3839,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D38" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B38&amp;"*")</f>
@@ -3841,13 +3858,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D39" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B39&amp;"*")</f>
@@ -3860,13 +3877,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B40" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C40" s="23" t="s">
         <v>311</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>308</v>
       </c>
       <c r="D40" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B40&amp;"*")</f>
@@ -3879,13 +3896,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D41" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B41&amp;"*")</f>
@@ -3898,13 +3915,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D42" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B42&amp;"*")</f>
@@ -3917,13 +3934,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D43" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B43&amp;"*")</f>
@@ -3936,13 +3953,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D44" s="24" t="n">
         <f aca="false">COUNTIF('Track Tags'!$G$5:$G$36,"*"&amp;B44&amp;"*")</f>
@@ -3955,7 +3972,7 @@
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
@@ -3995,61 +4012,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4058,32 +4075,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -4117,191 +4134,191 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B5" s="31" t="n">
         <f aca="false">COUNTA('Track Tags'!$B$5:$B$36)</f>
         <v>32</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B6" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$H$5:$H$36,"&gt;0")</f>
         <v>32</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B7" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$H$5:$H$36,0)</f>
         <v>0</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B8" s="31" t="n">
         <f aca="false">SUM('Track Tags'!$H$5:$H$36)</f>
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B9" s="32" t="n">
         <f aca="false">IFERROR(B8/B6,0)</f>
-        <v>12.375</v>
+        <v>12.5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B10" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Lyric book + workbook")</f>
         <v>21</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B11" s="31" t="n">
         <f aca="false">COUNTIF('Track Tags'!$I$5:$I$36,"Lyric book only")</f>
         <v>11</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B12" s="31" t="n">
         <f aca="false">COUNTA('Tag Dictionary'!$B$5:$B$44)</f>
         <v>40</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B13" s="31" t="n">
         <f aca="false">COUNTIF('Tag Dictionary'!$D$5:$D$44,"&gt;0")</f>
         <v>40</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="31" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$C$5:$C$36)-LEN(SUBSTITUTE('Track Tags'!$C$5:$C$36,",","")))+((LEN('Track Tags'!$C$5:$C$36)&gt;0)*1))</f>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="31" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$D$5:$D$36)-LEN(SUBSTITUTE('Track Tags'!$D$5:$D$36,",","")))+((LEN('Track Tags'!$D$5:$D$36)&gt;0)*1))</f>
         <v>91</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="31" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$E$5:$E$36)-LEN(SUBSTITUTE('Track Tags'!$E$5:$E$36,",","")))+((LEN('Track Tags'!$E$5:$E$36)&gt;0)*1))</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" s="31" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$F$5:$F$36)-LEN(SUBSTITUTE('Track Tags'!$F$5:$F$36,",","")))+((LEN('Track Tags'!$F$5:$F$36)&gt;0)*1))</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="31" t="n">
         <f aca="false">SUMPRODUCT((LEN('Track Tags'!$G$5:$G$36)-LEN(SUBSTITUTE('Track Tags'!$G$5:$G$36,",","")))+((LEN('Track Tags'!$G$5:$G$36)&gt;0)*1))</f>
         <v>67</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
